--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -23418,6 +23418,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1003">
+      <c r="A1003" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1003" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="G1003" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1004" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C1004" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="G1004" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -23464,6 +23464,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1005">
+      <c r="A1005" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1005" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1005" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="G1005" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -23487,6 +23487,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1006">
+      <c r="A1006" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1006" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C1006" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="G1006" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -23510,6 +23510,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1007">
+      <c r="A1007" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1007" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C1007" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="G1007" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -23351,22 +23351,22 @@
     </row>
     <row r="1000">
       <c r="A1000" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1000" t="n">
-        <v>8500</v>
+        <v>0</v>
       </c>
       <c r="C1000" t="n">
-        <v>5.80000019073486</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="D1000" t="n">
-        <v>5.65000009536743</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="E1000" t="n">
-        <v>5.80000019073486</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="F1000" t="n">
-        <v>5.80000019073486</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="G1000" t="s">
         <v>7</v>
@@ -23374,22 +23374,22 @@
     </row>
     <row r="1001">
       <c r="A1001" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1001" t="n">
-        <v>4500</v>
+        <v>8500</v>
       </c>
       <c r="C1001" t="n">
-        <v>5.90000009536743</v>
+        <v>5.80000019073486</v>
       </c>
       <c r="D1001" t="n">
-        <v>5.80000019073486</v>
+        <v>5.65000009536743</v>
       </c>
       <c r="E1001" t="n">
         <v>5.80000019073486</v>
       </c>
       <c r="F1001" t="n">
-        <v>5.90000009536743</v>
+        <v>5.80000019073486</v>
       </c>
       <c r="G1001" t="s">
         <v>7</v>
@@ -23397,16 +23397,16 @@
     </row>
     <row r="1002">
       <c r="A1002" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1002" t="n">
-        <v>19000</v>
+        <v>4500</v>
       </c>
       <c r="C1002" t="n">
-        <v>6</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="D1002" t="n">
-        <v>5.69999980926514</v>
+        <v>5.80000019073486</v>
       </c>
       <c r="E1002" t="n">
         <v>5.80000019073486</v>
@@ -23420,19 +23420,19 @@
     </row>
     <row r="1003">
       <c r="A1003" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1003" t="n">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="C1003" t="n">
-        <v>5.90000009536743</v>
+        <v>6</v>
       </c>
       <c r="D1003" t="n">
-        <v>5.90000009536743</v>
+        <v>5.69999980926514</v>
       </c>
       <c r="E1003" t="n">
-        <v>5.90000009536743</v>
+        <v>5.80000019073486</v>
       </c>
       <c r="F1003" t="n">
         <v>5.90000009536743</v>
@@ -23443,19 +23443,19 @@
     </row>
     <row r="1004">
       <c r="A1004" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1004" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="C1004" t="n">
         <v>5.90000009536743</v>
       </c>
       <c r="D1004" t="n">
-        <v>5.75</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="E1004" t="n">
-        <v>5.84999990463257</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="F1004" t="n">
         <v>5.90000009536743</v>
@@ -23466,16 +23466,16 @@
     </row>
     <row r="1005">
       <c r="A1005" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1005" t="n">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="C1005" t="n">
         <v>5.90000009536743</v>
       </c>
       <c r="D1005" t="n">
-        <v>5.80000019073486</v>
+        <v>5.75</v>
       </c>
       <c r="E1005" t="n">
         <v>5.84999990463257</v>
@@ -23489,22 +23489,22 @@
     </row>
     <row r="1006">
       <c r="A1006" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1006" t="n">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="C1006" t="n">
-        <v>5.94999980926514</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="D1006" t="n">
         <v>5.80000019073486</v>
       </c>
       <c r="E1006" t="n">
-        <v>5.94999980926514</v>
+        <v>5.84999990463257</v>
       </c>
       <c r="F1006" t="n">
-        <v>5.94999980926514</v>
+        <v>5.90000009536743</v>
       </c>
       <c r="G1006" t="s">
         <v>7</v>
@@ -23512,10 +23512,10 @@
     </row>
     <row r="1007">
       <c r="A1007" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1007" t="n">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="C1007" t="n">
         <v>5.94999980926514</v>
@@ -23527,9 +23527,32 @@
         <v>5.94999980926514</v>
       </c>
       <c r="F1007" t="n">
-        <v>5.80000019073486</v>
+        <v>5.94999980926514</v>
       </c>
       <c r="G1007" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1008" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1008" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="G1008" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -525,7 +525,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>3.76135683059692</v>
+        <v>3.76135659217834</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.64949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>3.5840916633606</v>
+        <v>3.58409190177917</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.1875</v>
       </c>
       <c r="G33" t="n">
-        <v>3.13037204742432</v>
+        <v>3.1303722858429</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>2.92659115791321</v>
+        <v>2.92659091949463</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G37" t="n">
-        <v>2.80874180793762</v>
+        <v>2.80874133110046</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82838320732117</v>
+        <v>2.82838344573975</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.82550001144409</v>
       </c>
       <c r="G40" t="n">
-        <v>2.7748601436615</v>
+        <v>2.77485990524292</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.25</v>
       </c>
       <c r="G43" t="n">
-        <v>3.19175219535828</v>
+        <v>3.1917519569397</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G45" t="n">
-        <v>3.32924270629883</v>
+        <v>3.32924294471741</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G48" t="n">
-        <v>3.35379481315613</v>
+        <v>3.35379457473755</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G49" t="n">
-        <v>3.33857226371765</v>
+        <v>3.33857250213623</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.28013896942139</v>
+        <v>3.28013873100281</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G51" t="n">
-        <v>3.28013896942139</v>
+        <v>3.28013873100281</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G52" t="n">
-        <v>3.28013896942139</v>
+        <v>3.28013873100281</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G54" t="n">
-        <v>3.22121405601501</v>
+        <v>3.22121429443359</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G56" t="n">
-        <v>3.18193125724792</v>
+        <v>3.18193101882935</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G74" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>2.98551559448242</v>
+        <v>2.985515832901</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G76" t="n">
-        <v>2.98551559448242</v>
+        <v>2.985515832901</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>2.98551559448242</v>
+        <v>2.985515832901</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.98551559448242</v>
+        <v>2.985515832901</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>2.9658739566803</v>
+        <v>2.96587419509888</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.06408190727234</v>
+        <v>3.06408166885376</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.06408190727234</v>
+        <v>3.06408166885376</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G92" t="n">
-        <v>3.09354400634766</v>
+        <v>3.09354448318481</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.09354400634766</v>
+        <v>3.09354448318481</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G94" t="n">
-        <v>3.06408190727234</v>
+        <v>3.06408166885376</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G95" t="n">
-        <v>3.21139335632324</v>
+        <v>3.21139359474182</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>2.9658739566803</v>
+        <v>2.96587419509888</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>3.00515699386597</v>
+        <v>3.00515723228455</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>3.00515699386597</v>
+        <v>3.00515723228455</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>2.98551559448242</v>
+        <v>2.985515832901</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>2.9658739566803</v>
+        <v>2.96587419509888</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G103" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G104" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G106" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>2.92659115791321</v>
+        <v>2.92659091949463</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>2.84802484512329</v>
+        <v>2.84802508354187</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>2.84802484512329</v>
+        <v>2.84802508354187</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>2.92659115791321</v>
+        <v>2.92659091949463</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G124" t="n">
-        <v>2.86766624450684</v>
+        <v>2.86766648292542</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>2.86766624450684</v>
+        <v>2.86766648292542</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>2.86766624450684</v>
+        <v>2.86766648292542</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>2.86766624450684</v>
+        <v>2.86766648292542</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>2.79892110824585</v>
+        <v>2.79892086982727</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>2.710533618927</v>
+        <v>2.71053385734558</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G131" t="n">
-        <v>2.74981689453125</v>
+        <v>2.74981713294983</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.74981689453125</v>
+        <v>2.74981713294983</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G133" t="n">
-        <v>2.65160942077637</v>
+        <v>2.65160918235779</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.72035479545593</v>
+        <v>2.72035455703735</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G136" t="n">
-        <v>3.08372330665588</v>
+        <v>3.08372354507446</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G137" t="n">
-        <v>3.08372330665588</v>
+        <v>3.08372354507446</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.09354400634766</v>
+        <v>3.09354448318481</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G145" t="n">
-        <v>3.08372330665588</v>
+        <v>3.08372354507446</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G148" t="n">
-        <v>3.07390260696411</v>
+        <v>3.07390284538269</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>3.28995966911316</v>
+        <v>3.28995943069458</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>3.15246891975403</v>
+        <v>3.15246868133545</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G158" t="n">
-        <v>3.05426120758057</v>
+        <v>3.05426073074341</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G159" t="n">
-        <v>3.05426120758057</v>
+        <v>3.05426073074341</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G162" t="n">
-        <v>3.06411361694336</v>
+        <v>3.06411337852478</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G163" t="n">
-        <v>3.06411361694336</v>
+        <v>3.06411337852478</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.33013010025024</v>
+        <v>3.33012986183167</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G165" t="n">
-        <v>3.33998227119446</v>
+        <v>3.33998250961304</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73408031463623</v>
+        <v>3.73408055305481</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G170" t="n">
-        <v>3.8227527141571</v>
+        <v>3.82275247573853</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G174" t="n">
-        <v>4.23655557632446</v>
+        <v>4.23655605316162</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G177" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>3.98039150238037</v>
+        <v>3.98039197921753</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>4.06906366348267</v>
+        <v>4.06906414031982</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G198" t="n">
-        <v>3.8227527141571</v>
+        <v>3.82275247573853</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>3.71437549591064</v>
+        <v>3.71437573432922</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G207" t="n">
-        <v>3.71437549591064</v>
+        <v>3.71437573432922</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G208" t="n">
-        <v>3.71437549591064</v>
+        <v>3.71437573432922</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>3.42865443229675</v>
+        <v>3.42865419387817</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G214" t="n">
-        <v>3.35968708992004</v>
+        <v>3.35968732833862</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G216" t="n">
-        <v>3.60599851608276</v>
+        <v>3.60599875450134</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>3.98039150238037</v>
+        <v>3.98039197921753</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G219" t="n">
-        <v>3.97053956985474</v>
+        <v>3.97053933143616</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>3.97053956985474</v>
+        <v>3.97053933143616</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G221" t="n">
-        <v>3.97053956985474</v>
+        <v>3.97053933143616</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06906366348267</v>
+        <v>4.06906414031982</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G223" t="n">
-        <v>4.06906366348267</v>
+        <v>4.06906414031982</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.25</v>
       </c>
       <c r="G225" t="n">
-        <v>4.1872935295105</v>
+        <v>4.18729305267334</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G228" t="n">
-        <v>3.93112969398499</v>
+        <v>3.93112945556641</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G229" t="n">
-        <v>3.93112969398499</v>
+        <v>3.93112945556641</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G230" t="n">
-        <v>4.00009679794312</v>
+        <v>4.00009632110596</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G231" t="n">
-        <v>4.00009679794312</v>
+        <v>4.00009632110596</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G232" t="n">
-        <v>4.00009679794312</v>
+        <v>4.00009632110596</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>3.98039150238037</v>
+        <v>3.98039197921753</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G237" t="n">
-        <v>3.98039150238037</v>
+        <v>3.98039197921753</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>3.98039150238037</v>
+        <v>3.98039197921753</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G272" t="n">
-        <v>3.53703141212463</v>
+        <v>3.53703117370605</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G273" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G275" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G290" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G293" t="n">
-        <v>3.40894961357117</v>
+        <v>3.40894937515259</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G294" t="n">
-        <v>3.35968708992004</v>
+        <v>3.35968732833862</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G301" t="n">
-        <v>3.47791647911072</v>
+        <v>3.4779167175293</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G302" t="n">
-        <v>3.47791647911072</v>
+        <v>3.4779167175293</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G304" t="n">
-        <v>3.53703141212463</v>
+        <v>3.53703117370605</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G305" t="n">
-        <v>3.66511344909668</v>
+        <v>3.6651132106781</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G314" t="n">
-        <v>3.98039150238037</v>
+        <v>3.98039197921753</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G319" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>4.07891654968262</v>
+        <v>4.07891607284546</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>4.06906366348267</v>
+        <v>4.06906414031982</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.25</v>
       </c>
       <c r="G336" t="n">
-        <v>4.1872935295105</v>
+        <v>4.18729305267334</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>4.33508062362671</v>
+        <v>4.33508014678955</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G343" t="n">
-        <v>4.26611328125</v>
+        <v>4.26611280441284</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G344" t="n">
-        <v>4.26611328125</v>
+        <v>4.26611280441284</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>4.26611328125</v>
+        <v>4.26611280441284</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.77353858947754</v>
+        <v>5.7735390663147</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G352" t="n">
-        <v>5.63560438156128</v>
+        <v>5.63560390472412</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G357" t="n">
-        <v>5.67501401901245</v>
+        <v>5.67501449584961</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G358" t="n">
-        <v>5.67501401901245</v>
+        <v>5.67501449584961</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G362" t="n">
-        <v>5.26121091842651</v>
+        <v>5.26121139526367</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G371" t="n">
-        <v>5.67501401901245</v>
+        <v>5.67501449584961</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>5.73412895202637</v>
+        <v>5.73412942886353</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>5.61589956283569</v>
+        <v>5.61589908599854</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.61589956283569</v>
+        <v>5.61589908599854</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G376" t="n">
-        <v>5.73412895202637</v>
+        <v>5.73412942886353</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>5.65530920028687</v>
+        <v>5.65530872344971</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G380" t="n">
-        <v>5.65530920028687</v>
+        <v>5.65530872344971</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G381" t="n">
-        <v>5.65530920028687</v>
+        <v>5.65530872344971</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>5.51737451553345</v>
+        <v>5.51737499237061</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>5.61589956283569</v>
+        <v>5.61589908599854</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>6.20704650878906</v>
+        <v>6.20704698562622</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.5</v>
       </c>
       <c r="G405" t="n">
-        <v>6.4040961265564</v>
+        <v>6.40409564971924</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.5</v>
       </c>
       <c r="G406" t="n">
-        <v>6.4040961265564</v>
+        <v>6.40409564971924</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.5</v>
       </c>
       <c r="G407" t="n">
-        <v>6.4040961265564</v>
+        <v>6.40409564971924</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.5</v>
       </c>
       <c r="G408" t="n">
-        <v>6.4040961265564</v>
+        <v>6.40409564971924</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.5</v>
       </c>
       <c r="G410" t="n">
-        <v>6.4040961265564</v>
+        <v>6.40409564971924</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>6.5</v>
       </c>
       <c r="G412" t="n">
-        <v>6.4040961265564</v>
+        <v>6.40409564971924</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -26632,6 +26632,32 @@
         <v>5.94999980926514</v>
       </c>
       <c r="H1010" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1011" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1011" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1011" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -525,7 +525,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>3.76135659217834</v>
+        <v>3.76135683059692</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.64949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>3.58409190177917</v>
+        <v>3.5840916633606</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.1875</v>
       </c>
       <c r="G33" t="n">
-        <v>3.1303722858429</v>
+        <v>3.13037204742432</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>2.92659091949463</v>
+        <v>2.92659115791321</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G37" t="n">
-        <v>2.80874133110046</v>
+        <v>2.80874180793762</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82838344573975</v>
+        <v>2.82838320732117</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.82550001144409</v>
       </c>
       <c r="G40" t="n">
-        <v>2.77485990524292</v>
+        <v>2.7748601436615</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.25</v>
       </c>
       <c r="G43" t="n">
-        <v>3.1917519569397</v>
+        <v>3.19175219535828</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G45" t="n">
-        <v>3.32924294471741</v>
+        <v>3.32924270629883</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G48" t="n">
-        <v>3.35379457473755</v>
+        <v>3.35379481315613</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G49" t="n">
-        <v>3.33857250213623</v>
+        <v>3.33857226371765</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.28013873100281</v>
+        <v>3.28013896942139</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G51" t="n">
-        <v>3.28013873100281</v>
+        <v>3.28013896942139</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G52" t="n">
-        <v>3.28013873100281</v>
+        <v>3.28013896942139</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G54" t="n">
-        <v>3.22121429443359</v>
+        <v>3.22121405601501</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G56" t="n">
-        <v>3.18193101882935</v>
+        <v>3.18193125724792</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G74" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G76" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.06408166885376</v>
+        <v>3.06408190727234</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.06408166885376</v>
+        <v>3.06408190727234</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G92" t="n">
-        <v>3.09354448318481</v>
+        <v>3.09354400634766</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.09354448318481</v>
+        <v>3.09354400634766</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G94" t="n">
-        <v>3.06408166885376</v>
+        <v>3.06408190727234</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G95" t="n">
-        <v>3.21139359474182</v>
+        <v>3.21139335632324</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>3.00515723228455</v>
+        <v>3.00515699386597</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>3.00515723228455</v>
+        <v>3.00515699386597</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G103" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G104" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G106" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>2.92659091949463</v>
+        <v>2.92659115791321</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>2.84802508354187</v>
+        <v>2.84802484512329</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>2.84802508354187</v>
+        <v>2.84802484512329</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>2.92659091949463</v>
+        <v>2.92659115791321</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G124" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>2.79892086982727</v>
+        <v>2.79892110824585</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>2.71053385734558</v>
+        <v>2.710533618927</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G131" t="n">
-        <v>2.74981713294983</v>
+        <v>2.74981689453125</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.74981713294983</v>
+        <v>2.74981689453125</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G133" t="n">
-        <v>2.65160918235779</v>
+        <v>2.65160942077637</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.72035455703735</v>
+        <v>2.72035479545593</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G136" t="n">
-        <v>3.08372354507446</v>
+        <v>3.08372330665588</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G137" t="n">
-        <v>3.08372354507446</v>
+        <v>3.08372330665588</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.09354448318481</v>
+        <v>3.09354400634766</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G145" t="n">
-        <v>3.08372354507446</v>
+        <v>3.08372330665588</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G148" t="n">
-        <v>3.07390284538269</v>
+        <v>3.07390260696411</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>3.28995943069458</v>
+        <v>3.28995966911316</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>3.15246868133545</v>
+        <v>3.15246891975403</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G158" t="n">
-        <v>3.05426073074341</v>
+        <v>3.05426120758057</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G159" t="n">
-        <v>3.05426073074341</v>
+        <v>3.05426120758057</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G162" t="n">
-        <v>3.06411337852478</v>
+        <v>3.06411361694336</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G163" t="n">
-        <v>3.06411337852478</v>
+        <v>3.06411361694336</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.33012986183167</v>
+        <v>3.33013010025024</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G165" t="n">
-        <v>3.33998250961304</v>
+        <v>3.33998227119446</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73408055305481</v>
+        <v>3.73408031463623</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G170" t="n">
-        <v>3.82275247573853</v>
+        <v>3.8227527141571</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G174" t="n">
-        <v>4.23655605316162</v>
+        <v>4.23655557632446</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G177" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G198" t="n">
-        <v>3.82275247573853</v>
+        <v>3.8227527141571</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>3.71437573432922</v>
+        <v>3.71437549591064</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G207" t="n">
-        <v>3.71437573432922</v>
+        <v>3.71437549591064</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G208" t="n">
-        <v>3.71437573432922</v>
+        <v>3.71437549591064</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>3.42865419387817</v>
+        <v>3.42865443229675</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G214" t="n">
-        <v>3.35968732833862</v>
+        <v>3.35968708992004</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G216" t="n">
-        <v>3.60599875450134</v>
+        <v>3.60599851608276</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G219" t="n">
-        <v>3.97053933143616</v>
+        <v>3.97053956985474</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>3.97053933143616</v>
+        <v>3.97053956985474</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G221" t="n">
-        <v>3.97053933143616</v>
+        <v>3.97053956985474</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G223" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.25</v>
       </c>
       <c r="G225" t="n">
-        <v>4.18729305267334</v>
+        <v>4.1872935295105</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G228" t="n">
-        <v>3.93112945556641</v>
+        <v>3.93112969398499</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G229" t="n">
-        <v>3.93112945556641</v>
+        <v>3.93112969398499</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G230" t="n">
-        <v>4.00009632110596</v>
+        <v>4.00009679794312</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G231" t="n">
-        <v>4.00009632110596</v>
+        <v>4.00009679794312</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G232" t="n">
-        <v>4.00009632110596</v>
+        <v>4.00009679794312</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G237" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G272" t="n">
-        <v>3.53703117370605</v>
+        <v>3.53703141212463</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G273" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G275" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G290" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G293" t="n">
-        <v>3.40894937515259</v>
+        <v>3.40894961357117</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G294" t="n">
-        <v>3.35968732833862</v>
+        <v>3.35968708992004</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G301" t="n">
-        <v>3.4779167175293</v>
+        <v>3.47791647911072</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G302" t="n">
-        <v>3.4779167175293</v>
+        <v>3.47791647911072</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G304" t="n">
-        <v>3.53703117370605</v>
+        <v>3.53703141212463</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G305" t="n">
-        <v>3.6651132106781</v>
+        <v>3.66511344909668</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G314" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G319" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>4.07891607284546</v>
+        <v>4.07891654968262</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.25</v>
       </c>
       <c r="G336" t="n">
-        <v>4.18729305267334</v>
+        <v>4.1872935295105</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>4.33508014678955</v>
+        <v>4.33508062362671</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G343" t="n">
-        <v>4.26611280441284</v>
+        <v>4.26611328125</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G344" t="n">
-        <v>4.26611280441284</v>
+        <v>4.26611328125</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>4.26611280441284</v>
+        <v>4.26611328125</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.7735390663147</v>
+        <v>5.77353858947754</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G352" t="n">
-        <v>5.63560390472412</v>
+        <v>5.63560438156128</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G357" t="n">
-        <v>5.67501449584961</v>
+        <v>5.67501401901245</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G358" t="n">
-        <v>5.67501449584961</v>
+        <v>5.67501401901245</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G362" t="n">
-        <v>5.26121139526367</v>
+        <v>5.26121091842651</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G371" t="n">
-        <v>5.67501449584961</v>
+        <v>5.67501401901245</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>5.73412942886353</v>
+        <v>5.73412895202637</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>5.61589908599854</v>
+        <v>5.61589956283569</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.61589908599854</v>
+        <v>5.61589956283569</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G376" t="n">
-        <v>5.73412942886353</v>
+        <v>5.73412895202637</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>5.65530872344971</v>
+        <v>5.65530920028687</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G380" t="n">
-        <v>5.65530872344971</v>
+        <v>5.65530920028687</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G381" t="n">
-        <v>5.65530872344971</v>
+        <v>5.65530920028687</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>5.51737499237061</v>
+        <v>5.51737451553345</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>5.61589908599854</v>
+        <v>5.61589956283569</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>6.20704698562622</v>
+        <v>6.20704650878906</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.5</v>
       </c>
       <c r="G405" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.5</v>
       </c>
       <c r="G406" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.5</v>
       </c>
       <c r="G407" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.5</v>
       </c>
       <c r="G408" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.5</v>
       </c>
       <c r="G410" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>6.5</v>
       </c>
       <c r="G412" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -26658,6 +26658,32 @@
         <v>6</v>
       </c>
       <c r="H1011" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1012" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1012" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="H1012" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -23740,6 +23740,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1017">
+      <c r="A1017" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1017" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="G1017" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B1018" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C1018" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="F1018"/>
+      <c r="G1018" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -23825,8 +23825,31 @@
       <c r="E1020" t="n">
         <v>6</v>
       </c>
-      <c r="F1020"/>
+      <c r="F1020" t="n">
+        <v>5.94999980926514</v>
+      </c>
       <c r="G1020" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1021" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1021" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="F1021"/>
+      <c r="G1021" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -23848,8 +23848,31 @@
       <c r="E1021" t="n">
         <v>5.94999980926514</v>
       </c>
-      <c r="F1021"/>
+      <c r="F1021" t="n">
+        <v>5.94999980926514</v>
+      </c>
       <c r="G1021" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1022" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C1022" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1022" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="F1022"/>
+      <c r="G1022" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -23871,8 +23871,31 @@
       <c r="E1022" t="n">
         <v>5.80000019073486</v>
       </c>
-      <c r="F1022"/>
+      <c r="F1022" t="n">
+        <v>5.84999990463257</v>
+      </c>
       <c r="G1022" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1023" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1023" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="F1023"/>
+      <c r="G1023" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -23894,7 +23894,9 @@
       <c r="E1023" t="n">
         <v>5.90000009536743</v>
       </c>
-      <c r="F1023"/>
+      <c r="F1023" t="n">
+        <v>5.90000009536743</v>
+      </c>
       <c r="G1023" t="s">
         <v>7</v>
       </c>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -23924,6 +23924,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1025">
+      <c r="A1025" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1025" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1025" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="G1025" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2" t="n">
-        <v>3.14264822006226</v>
+        <v>3.14264798164368</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G4" t="n">
-        <v>3.67297005653381</v>
+        <v>3.67296981811523</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>3.76135659217834</v>
+        <v>3.76135683059692</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.8585000038147</v>
       </c>
       <c r="G12" t="n">
-        <v>3.78934621810913</v>
+        <v>3.78934597969055</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.71716356277466</v>
+        <v>3.71716380119324</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65332841873169</v>
+        <v>3.65332818031311</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G17" t="n">
-        <v>3.65332841873169</v>
+        <v>3.65332818031311</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>3.63368678092957</v>
+        <v>3.63368701934814</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>3.58458304405212</v>
+        <v>3.58458280563354</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G24" t="n">
-        <v>3.57476210594177</v>
+        <v>3.57476234436035</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.50049996376038</v>
       </c>
       <c r="G28" t="n">
-        <v>3.43776226043701</v>
+        <v>3.43776249885559</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>3.38816738128662</v>
+        <v>3.3881676197052</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G34" t="n">
-        <v>2.98747992515564</v>
+        <v>2.98747968673706</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G37" t="n">
-        <v>2.80874133110046</v>
+        <v>2.80874156951904</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83820390701294</v>
+        <v>2.83820414543152</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>2.82550001144409</v>
       </c>
       <c r="G40" t="n">
-        <v>2.77485990524292</v>
+        <v>2.7748601436615</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.24085569381714</v>
+        <v>3.24085593223572</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>3.37834668159485</v>
+        <v>3.37834644317627</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>3.43727135658264</v>
+        <v>3.43727111816406</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G48" t="n">
-        <v>3.35379457473755</v>
+        <v>3.35379481315613</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.28013873100281</v>
+        <v>3.28013896942139</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G51" t="n">
-        <v>3.28013873100281</v>
+        <v>3.28013896942139</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G52" t="n">
-        <v>3.28013873100281</v>
+        <v>3.28013896942139</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.29978036880493</v>
+        <v>3.29978013038635</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G54" t="n">
-        <v>3.22121429443359</v>
+        <v>3.22121405601501</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G55" t="n">
-        <v>3.26049709320068</v>
+        <v>3.26049733161926</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G56" t="n">
-        <v>3.18193101882935</v>
+        <v>3.18193125724792</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14264822006226</v>
+        <v>3.14264798164368</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.01497793197632</v>
+        <v>3.01497769355774</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.01497793197632</v>
+        <v>3.01497769355774</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G76" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.06408166885376</v>
+        <v>3.06408190727234</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.06408166885376</v>
+        <v>3.06408190727234</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G90" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G92" t="n">
-        <v>3.09354448318481</v>
+        <v>3.09354424476624</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.09354448318481</v>
+        <v>3.09354424476624</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G94" t="n">
-        <v>3.06408166885376</v>
+        <v>3.06408190727234</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>3.00515723228455</v>
+        <v>3.00515699386597</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>3.00515723228455</v>
+        <v>3.00515699386597</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>2.84802508354187</v>
+        <v>2.84802484512329</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>2.84802508354187</v>
+        <v>2.84802484512329</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G111" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G112" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G113" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G114" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G115" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G119" t="n">
-        <v>2.83820390701294</v>
+        <v>2.83820414543152</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G120" t="n">
-        <v>2.83820390701294</v>
+        <v>2.83820414543152</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G124" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>2.79892086982727</v>
+        <v>2.79892063140869</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G136" t="n">
-        <v>3.08372354507446</v>
+        <v>3.08372330665588</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G137" t="n">
-        <v>3.08372354507446</v>
+        <v>3.08372330665588</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G138" t="n">
-        <v>3.10336494445801</v>
+        <v>3.10336518287659</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.09354448318481</v>
+        <v>3.09354424476624</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.1328272819519</v>
+        <v>3.13282752037048</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G142" t="n">
-        <v>3.01497793197632</v>
+        <v>3.01497769355774</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G143" t="n">
-        <v>3.01497793197632</v>
+        <v>3.01497769355774</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G144" t="n">
-        <v>2.99533629417419</v>
+        <v>2.99533653259277</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G145" t="n">
-        <v>3.08372354507446</v>
+        <v>3.08372330665588</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G148" t="n">
-        <v>3.07390284538269</v>
+        <v>3.07390260696411</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>3.23103499412537</v>
+        <v>3.23103475570679</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>3.23103499412537</v>
+        <v>3.23103475570679</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>3.14264822006226</v>
+        <v>3.14264798164368</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G158" t="n">
-        <v>3.05426073074341</v>
+        <v>3.05426096916199</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G159" t="n">
-        <v>3.05426073074341</v>
+        <v>3.05426096916199</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G162" t="n">
-        <v>3.06411337852478</v>
+        <v>3.06411361694336</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G163" t="n">
-        <v>3.06411337852478</v>
+        <v>3.06411361694336</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.33012986183167</v>
+        <v>3.33013010025024</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G165" t="n">
-        <v>3.33998250961304</v>
+        <v>3.33998227119446</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73408055305481</v>
+        <v>3.73408031463623</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G170" t="n">
-        <v>3.82275247573853</v>
+        <v>3.8227527141571</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G174" t="n">
-        <v>4.23655605316162</v>
+        <v>4.23655557632446</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G177" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G198" t="n">
-        <v>3.82275247573853</v>
+        <v>3.8227527141571</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>3.71437573432922</v>
+        <v>3.71437549591064</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G207" t="n">
-        <v>3.71437573432922</v>
+        <v>3.71437549591064</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G208" t="n">
-        <v>3.71437573432922</v>
+        <v>3.71437549591064</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>3.42865419387817</v>
+        <v>3.42865443229675</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G214" t="n">
-        <v>3.35968732833862</v>
+        <v>3.35968708992004</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G216" t="n">
-        <v>3.60599875450134</v>
+        <v>3.60599851608276</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G219" t="n">
-        <v>3.97053933143616</v>
+        <v>3.97053956985474</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>3.97053933143616</v>
+        <v>3.97053956985474</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G221" t="n">
-        <v>3.97053933143616</v>
+        <v>3.97053956985474</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G223" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.25</v>
       </c>
       <c r="G225" t="n">
-        <v>4.18729305267334</v>
+        <v>4.1872935295105</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G228" t="n">
-        <v>3.93112945556641</v>
+        <v>3.93112969398499</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G229" t="n">
-        <v>3.93112945556641</v>
+        <v>3.93112969398499</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G230" t="n">
-        <v>4.00009632110596</v>
+        <v>4.00009679794312</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G231" t="n">
-        <v>4.00009632110596</v>
+        <v>4.00009679794312</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G232" t="n">
-        <v>4.00009632110596</v>
+        <v>4.00009679794312</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G237" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G272" t="n">
-        <v>3.53703117370605</v>
+        <v>3.53703141212463</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G273" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G275" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G290" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G293" t="n">
-        <v>3.40894937515259</v>
+        <v>3.40894961357117</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G294" t="n">
-        <v>3.35968732833862</v>
+        <v>3.35968708992004</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G301" t="n">
-        <v>3.4779167175293</v>
+        <v>3.47791647911072</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G302" t="n">
-        <v>3.4779167175293</v>
+        <v>3.47791647911072</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G304" t="n">
-        <v>3.53703117370605</v>
+        <v>3.53703141212463</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G305" t="n">
-        <v>3.6651132106781</v>
+        <v>3.66511344909668</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G314" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G319" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>4.07891607284546</v>
+        <v>4.07891654968262</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.25</v>
       </c>
       <c r="G336" t="n">
-        <v>4.18729305267334</v>
+        <v>4.1872935295105</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>4.33508014678955</v>
+        <v>4.33508062362671</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G343" t="n">
-        <v>4.26611280441284</v>
+        <v>4.26611328125</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G344" t="n">
-        <v>4.26611280441284</v>
+        <v>4.26611328125</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>4.26611280441284</v>
+        <v>4.26611328125</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.7735390663147</v>
+        <v>5.77353858947754</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G352" t="n">
-        <v>5.63560390472412</v>
+        <v>5.63560438156128</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G357" t="n">
-        <v>5.67501449584961</v>
+        <v>5.67501401901245</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G358" t="n">
-        <v>5.67501449584961</v>
+        <v>5.67501401901245</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G362" t="n">
-        <v>5.26121139526367</v>
+        <v>5.26121091842651</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G371" t="n">
-        <v>5.67501449584961</v>
+        <v>5.67501401901245</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>5.73412942886353</v>
+        <v>5.73412895202637</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>5.61589908599854</v>
+        <v>5.61589956283569</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.61589908599854</v>
+        <v>5.61589956283569</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G376" t="n">
-        <v>5.73412942886353</v>
+        <v>5.73412895202637</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>5.65530872344971</v>
+        <v>5.65530920028687</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G380" t="n">
-        <v>5.65530872344971</v>
+        <v>5.65530920028687</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G381" t="n">
-        <v>5.65530872344971</v>
+        <v>5.65530920028687</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>5.51737499237061</v>
+        <v>5.51737451553345</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>5.61589908599854</v>
+        <v>5.61589956283569</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>6.20704698562622</v>
+        <v>6.20704650878906</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.5</v>
       </c>
       <c r="G405" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.5</v>
       </c>
       <c r="G406" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.5</v>
       </c>
       <c r="G407" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.5</v>
       </c>
       <c r="G408" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.5</v>
       </c>
       <c r="G410" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>6.5</v>
       </c>
       <c r="G412" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -27074,6 +27074,32 @@
         <v>6.05000019073486</v>
       </c>
       <c r="H1027" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1028" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1028" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="H1028" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -27103,6 +27103,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1029">
+      <c r="A1029" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1029" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1029" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="H1029" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2" t="n">
-        <v>3.14264822006226</v>
+        <v>3.14264798164368</v>
       </c>
       <c r="H2" t="n">
         <v>26500</v>
@@ -485,7 +485,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G4" t="n">
-        <v>3.67297005653381</v>
+        <v>3.67296981811523</v>
       </c>
       <c r="H4" t="n">
         <v>18000</v>
@@ -543,7 +543,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G6" t="n">
-        <v>3.76135659217834</v>
+        <v>3.76135683059692</v>
       </c>
       <c r="H6" t="n">
         <v>1500</v>
@@ -572,7 +572,7 @@
         <v>3.75</v>
       </c>
       <c r="G7" t="n">
-        <v>3.68279075622559</v>
+        <v>3.68279051780701</v>
       </c>
       <c r="H7" t="n">
         <v>5500</v>
@@ -659,7 +659,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G10" t="n">
-        <v>3.89884781837463</v>
+        <v>3.89884757995605</v>
       </c>
       <c r="H10" t="n">
         <v>36500</v>
@@ -775,7 +775,7 @@
         <v>3.75</v>
       </c>
       <c r="G14" t="n">
-        <v>3.68279075622559</v>
+        <v>3.68279051780701</v>
       </c>
       <c r="H14" t="n">
         <v>500</v>
@@ -891,7 +891,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>3.63368678092957</v>
+        <v>3.63368701934814</v>
       </c>
       <c r="H18" t="n">
         <v>2500</v>
@@ -1007,7 +1007,7 @@
         <v>3.75</v>
       </c>
       <c r="G22" t="n">
-        <v>3.68279075622559</v>
+        <v>3.68279051780701</v>
       </c>
       <c r="H22" t="n">
         <v>5500</v>
@@ -1036,7 +1036,7 @@
         <v>3.64949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>3.58409190177917</v>
+        <v>3.5840916633606</v>
       </c>
       <c r="H23" t="n">
         <v>1500</v>
@@ -1065,7 +1065,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G24" t="n">
-        <v>3.57476210594177</v>
+        <v>3.57476234436035</v>
       </c>
       <c r="H24" t="n">
         <v>5000</v>
@@ -1268,7 +1268,7 @@
         <v>3.28900003433228</v>
       </c>
       <c r="G31" t="n">
-        <v>3.23005294799805</v>
+        <v>3.23005270957947</v>
       </c>
       <c r="H31" t="n">
         <v>6000</v>
@@ -1413,7 +1413,7 @@
         <v>2.98699998855591</v>
       </c>
       <c r="G36" t="n">
-        <v>2.93346548080444</v>
+        <v>2.93346571922302</v>
       </c>
       <c r="H36" t="n">
         <v>14000</v>
@@ -1442,7 +1442,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G37" t="n">
-        <v>2.80874133110046</v>
+        <v>2.80874156951904</v>
       </c>
       <c r="H37" t="n">
         <v>12500</v>
@@ -1471,7 +1471,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83820390701294</v>
+        <v>2.83820414543152</v>
       </c>
       <c r="H38" t="n">
         <v>90500</v>
@@ -1529,7 +1529,7 @@
         <v>2.82550001144409</v>
       </c>
       <c r="G40" t="n">
-        <v>2.77485990524292</v>
+        <v>2.7748601436615</v>
       </c>
       <c r="H40" t="n">
         <v>500</v>
@@ -1732,7 +1732,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>3.43727135658264</v>
+        <v>3.43727111816406</v>
       </c>
       <c r="H47" t="n">
         <v>10500</v>
@@ -1761,7 +1761,7 @@
         <v>3.41499996185303</v>
       </c>
       <c r="G48" t="n">
-        <v>3.35379457473755</v>
+        <v>3.35379481315613</v>
       </c>
       <c r="H48" t="n">
         <v>33000</v>
@@ -1790,7 +1790,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G49" t="n">
-        <v>3.33857250213623</v>
+        <v>3.33857226371765</v>
       </c>
       <c r="H49" t="n">
         <v>12500</v>
@@ -1819,7 +1819,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.28013873100281</v>
+        <v>3.28013896942139</v>
       </c>
       <c r="H50" t="n">
         <v>1000</v>
@@ -1848,7 +1848,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G51" t="n">
-        <v>3.28013873100281</v>
+        <v>3.28013896942139</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G52" t="n">
-        <v>3.28013873100281</v>
+        <v>3.28013896942139</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.29978036880493</v>
+        <v>3.29978013038635</v>
       </c>
       <c r="H53" t="n">
         <v>2500</v>
@@ -1935,7 +1935,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G54" t="n">
-        <v>3.22121429443359</v>
+        <v>3.22121405601501</v>
       </c>
       <c r="H54" t="n">
         <v>1000</v>
@@ -1964,7 +1964,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G55" t="n">
-        <v>3.26049709320068</v>
+        <v>3.26049733161926</v>
       </c>
       <c r="H55" t="n">
         <v>500</v>
@@ -1993,7 +1993,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G56" t="n">
-        <v>3.18193101882935</v>
+        <v>3.18193125724792</v>
       </c>
       <c r="H56" t="n">
         <v>1000</v>
@@ -2196,7 +2196,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14264822006226</v>
+        <v>3.14264798164368</v>
       </c>
       <c r="H63" t="n">
         <v>2500</v>
@@ -2399,7 +2399,7 @@
         <v>3</v>
       </c>
       <c r="G70" t="n">
-        <v>2.94623231887817</v>
+        <v>2.94623255729675</v>
       </c>
       <c r="H70" t="n">
         <v>2500</v>
@@ -2428,7 +2428,7 @@
         <v>3</v>
       </c>
       <c r="G71" t="n">
-        <v>2.94623231887817</v>
+        <v>2.94623255729675</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>2.94623231887817</v>
+        <v>2.94623255729675</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G74" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H74" t="n">
         <v>1000</v>
@@ -2544,7 +2544,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H75" t="n">
         <v>1000</v>
@@ -2573,7 +2573,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G76" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2602,7 +2602,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G77" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H81" t="n">
         <v>500</v>
@@ -2747,7 +2747,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.06408166885376</v>
+        <v>3.06408190727234</v>
       </c>
       <c r="H82" t="n">
         <v>5000</v>
@@ -2776,7 +2776,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.06408166885376</v>
+        <v>3.06408190727234</v>
       </c>
       <c r="H83" t="n">
         <v>6500</v>
@@ -3037,7 +3037,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G92" t="n">
-        <v>3.09354448318481</v>
+        <v>3.09354400634766</v>
       </c>
       <c r="H92" t="n">
         <v>1000</v>
@@ -3066,7 +3066,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.09354448318481</v>
+        <v>3.09354400634766</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G94" t="n">
-        <v>3.06408166885376</v>
+        <v>3.06408190727234</v>
       </c>
       <c r="H94" t="n">
         <v>13500</v>
@@ -3211,7 +3211,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H98" t="n">
         <v>8000</v>
@@ -3240,7 +3240,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>3.00515723228455</v>
+        <v>3.00515699386597</v>
       </c>
       <c r="H99" t="n">
         <v>16000</v>
@@ -3269,7 +3269,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>3.00515723228455</v>
+        <v>3.00515699386597</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G101" t="n">
-        <v>2.985515832901</v>
+        <v>2.98551559448242</v>
       </c>
       <c r="H101" t="n">
         <v>5500</v>
@@ -3327,7 +3327,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H102" t="n">
         <v>4500</v>
@@ -3356,7 +3356,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G103" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H103" t="n">
         <v>1000</v>
@@ -3385,7 +3385,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G104" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G106" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G119" t="n">
-        <v>2.83820390701294</v>
+        <v>2.83820414543152</v>
       </c>
       <c r="H119" t="n">
         <v>4000</v>
@@ -3849,7 +3849,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G120" t="n">
-        <v>2.83820390701294</v>
+        <v>2.83820414543152</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G124" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H124" t="n">
         <v>2000</v>
@@ -3994,7 +3994,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>2.71053385734558</v>
+        <v>2.710533618927</v>
       </c>
       <c r="H130" t="n">
         <v>6500</v>
@@ -4168,7 +4168,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G131" t="n">
-        <v>2.74981713294983</v>
+        <v>2.74981689453125</v>
       </c>
       <c r="H131" t="n">
         <v>2000</v>
@@ -4197,7 +4197,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.74981713294983</v>
+        <v>2.74981689453125</v>
       </c>
       <c r="H132" t="n">
         <v>500</v>
@@ -4255,7 +4255,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.72035455703735</v>
+        <v>2.72035479545593</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4313,7 +4313,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G136" t="n">
-        <v>3.08372354507446</v>
+        <v>3.08372330665588</v>
       </c>
       <c r="H136" t="n">
         <v>50500</v>
@@ -4342,7 +4342,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G137" t="n">
-        <v>3.08372354507446</v>
+        <v>3.08372330665588</v>
       </c>
       <c r="H137" t="n">
         <v>39500</v>
@@ -4371,7 +4371,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G138" t="n">
-        <v>3.10336494445801</v>
+        <v>3.10336518287659</v>
       </c>
       <c r="H138" t="n">
         <v>4500</v>
@@ -4400,7 +4400,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.09354448318481</v>
+        <v>3.09354400634766</v>
       </c>
       <c r="H139" t="n">
         <v>6000</v>
@@ -4545,7 +4545,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G144" t="n">
-        <v>2.99533629417419</v>
+        <v>2.99533653259277</v>
       </c>
       <c r="H144" t="n">
         <v>3000</v>
@@ -4574,7 +4574,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G145" t="n">
-        <v>3.08372354507446</v>
+        <v>3.08372330665588</v>
       </c>
       <c r="H145" t="n">
         <v>17500</v>
@@ -4661,7 +4661,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G148" t="n">
-        <v>3.07390284538269</v>
+        <v>3.07390260696411</v>
       </c>
       <c r="H148" t="n">
         <v>3000</v>
@@ -4835,7 +4835,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>3.15246868133545</v>
+        <v>3.15246891975403</v>
       </c>
       <c r="H154" t="n">
         <v>5500</v>
@@ -4864,7 +4864,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>3.14264822006226</v>
+        <v>3.14264798164368</v>
       </c>
       <c r="H155" t="n">
         <v>3500</v>
@@ -4951,7 +4951,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G158" t="n">
-        <v>3.05426073074341</v>
+        <v>3.05426120758057</v>
       </c>
       <c r="H158" t="n">
         <v>3500</v>
@@ -4980,7 +4980,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G159" t="n">
-        <v>3.05426073074341</v>
+        <v>3.05426120758057</v>
       </c>
       <c r="H159" t="n">
         <v>500</v>
@@ -5067,7 +5067,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G162" t="n">
-        <v>3.06411337852478</v>
+        <v>3.06411361694336</v>
       </c>
       <c r="H162" t="n">
         <v>5500</v>
@@ -5096,7 +5096,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G163" t="n">
-        <v>3.06411337852478</v>
+        <v>3.06411361694336</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.33012986183167</v>
+        <v>3.33013010025024</v>
       </c>
       <c r="H164" t="n">
         <v>30000</v>
@@ -5154,7 +5154,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G165" t="n">
-        <v>3.33998250961304</v>
+        <v>3.33998227119446</v>
       </c>
       <c r="H165" t="n">
         <v>15500</v>
@@ -5270,7 +5270,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73408055305481</v>
+        <v>3.73408031463623</v>
       </c>
       <c r="H169" t="n">
         <v>17500</v>
@@ -5299,7 +5299,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G170" t="n">
-        <v>3.82275247573853</v>
+        <v>3.8227527141571</v>
       </c>
       <c r="H170" t="n">
         <v>16000</v>
@@ -5415,7 +5415,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G174" t="n">
-        <v>4.23655605316162</v>
+        <v>4.23655557632446</v>
       </c>
       <c r="H174" t="n">
         <v>14500</v>
@@ -5502,7 +5502,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G177" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H177" t="n">
         <v>3000</v>
@@ -5531,7 +5531,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H182" t="n">
         <v>4000</v>
@@ -5676,7 +5676,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H185" t="n">
         <v>1000</v>
@@ -5763,7 +5763,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H186" t="n">
         <v>3500</v>
@@ -6111,7 +6111,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G198" t="n">
-        <v>3.82275247573853</v>
+        <v>3.8227527141571</v>
       </c>
       <c r="H198" t="n">
         <v>5000</v>
@@ -6285,7 +6285,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H204" t="n">
         <v>2000</v>
@@ -6343,7 +6343,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>3.71437573432922</v>
+        <v>3.71437549591064</v>
       </c>
       <c r="H206" t="n">
         <v>1000</v>
@@ -6372,7 +6372,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G207" t="n">
-        <v>3.71437573432922</v>
+        <v>3.71437549591064</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G208" t="n">
-        <v>3.71437573432922</v>
+        <v>3.71437549591064</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>3.42865419387817</v>
+        <v>3.42865443229675</v>
       </c>
       <c r="H213" t="n">
         <v>2000</v>
@@ -6575,7 +6575,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G214" t="n">
-        <v>3.35968732833862</v>
+        <v>3.35968708992004</v>
       </c>
       <c r="H214" t="n">
         <v>4500</v>
@@ -6633,7 +6633,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G216" t="n">
-        <v>3.60599875450134</v>
+        <v>3.60599851608276</v>
       </c>
       <c r="H216" t="n">
         <v>13000</v>
@@ -6691,7 +6691,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H218" t="n">
         <v>16500</v>
@@ -6720,7 +6720,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G219" t="n">
-        <v>3.97053933143616</v>
+        <v>3.97053956985474</v>
       </c>
       <c r="H219" t="n">
         <v>8000</v>
@@ -6749,7 +6749,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>3.97053933143616</v>
+        <v>3.97053956985474</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G221" t="n">
-        <v>3.97053933143616</v>
+        <v>3.97053956985474</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H222" t="n">
         <v>3500</v>
@@ -6836,7 +6836,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G223" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H223" t="n">
         <v>6000</v>
@@ -6894,7 +6894,7 @@
         <v>4.25</v>
       </c>
       <c r="G225" t="n">
-        <v>4.18729305267334</v>
+        <v>4.1872935295105</v>
       </c>
       <c r="H225" t="n">
         <v>4000</v>
@@ -6981,7 +6981,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G228" t="n">
-        <v>3.93112945556641</v>
+        <v>3.93112969398499</v>
       </c>
       <c r="H228" t="n">
         <v>10000</v>
@@ -7010,7 +7010,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G229" t="n">
-        <v>3.93112945556641</v>
+        <v>3.93112969398499</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G230" t="n">
-        <v>4.00009632110596</v>
+        <v>4.00009679794312</v>
       </c>
       <c r="H230" t="n">
         <v>500</v>
@@ -7068,7 +7068,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G231" t="n">
-        <v>4.00009632110596</v>
+        <v>4.00009679794312</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G232" t="n">
-        <v>4.00009632110596</v>
+        <v>4.00009679794312</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H236" t="n">
         <v>2000</v>
@@ -7242,7 +7242,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G237" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H241" t="n">
         <v>1500</v>
@@ -7416,7 +7416,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H243" t="n">
         <v>5000</v>
@@ -7880,7 +7880,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H259" t="n">
         <v>13500</v>
@@ -8054,7 +8054,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H265" t="n">
         <v>1000</v>
@@ -8257,7 +8257,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G272" t="n">
-        <v>3.53703117370605</v>
+        <v>3.53703141212463</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8286,7 +8286,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G273" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H273" t="n">
         <v>8000</v>
@@ -8315,7 +8315,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H274" t="n">
         <v>500</v>
@@ -8344,7 +8344,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G275" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H289" t="n">
         <v>4500</v>
@@ -8779,7 +8779,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G290" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G293" t="n">
-        <v>3.40894937515259</v>
+        <v>3.40894961357117</v>
       </c>
       <c r="H293" t="n">
         <v>13000</v>
@@ -8895,7 +8895,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G294" t="n">
-        <v>3.35968732833862</v>
+        <v>3.35968708992004</v>
       </c>
       <c r="H294" t="n">
         <v>7500</v>
@@ -9098,7 +9098,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G301" t="n">
-        <v>3.4779167175293</v>
+        <v>3.47791647911072</v>
       </c>
       <c r="H301" t="n">
         <v>500</v>
@@ -9127,7 +9127,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G302" t="n">
-        <v>3.4779167175293</v>
+        <v>3.47791647911072</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G304" t="n">
-        <v>3.53703117370605</v>
+        <v>3.53703141212463</v>
       </c>
       <c r="H304" t="n">
         <v>7000</v>
@@ -9214,7 +9214,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G305" t="n">
-        <v>3.6651132106781</v>
+        <v>3.66511344909668</v>
       </c>
       <c r="H305" t="n">
         <v>15000</v>
@@ -9359,7 +9359,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H310" t="n">
         <v>6000</v>
@@ -9417,7 +9417,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H312" t="n">
         <v>1000</v>
@@ -9446,7 +9446,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H313" t="n">
         <v>1500</v>
@@ -9475,7 +9475,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G314" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H314" t="n">
         <v>3000</v>
@@ -9620,7 +9620,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G319" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H319" t="n">
         <v>2000</v>
@@ -9649,7 +9649,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H321" t="n">
         <v>4000</v>
@@ -9997,7 +9997,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>4.07891607284546</v>
+        <v>4.07891654968262</v>
       </c>
       <c r="H332" t="n">
         <v>5000</v>
@@ -10055,7 +10055,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H334" t="n">
         <v>10000</v>
@@ -10113,7 +10113,7 @@
         <v>4.25</v>
       </c>
       <c r="G336" t="n">
-        <v>4.18729305267334</v>
+        <v>4.1872935295105</v>
       </c>
       <c r="H336" t="n">
         <v>6500</v>
@@ -10171,7 +10171,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>4.33508014678955</v>
+        <v>4.33508062362671</v>
       </c>
       <c r="H338" t="n">
         <v>1000</v>
@@ -10316,7 +10316,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G343" t="n">
-        <v>4.26611280441284</v>
+        <v>4.26611328125</v>
       </c>
       <c r="H343" t="n">
         <v>1000</v>
@@ -10345,7 +10345,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G344" t="n">
-        <v>4.26611280441284</v>
+        <v>4.26611328125</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>4.26611280441284</v>
+        <v>4.26611328125</v>
       </c>
       <c r="H345" t="n">
         <v>1000</v>
@@ -10519,7 +10519,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.7735390663147</v>
+        <v>5.77353858947754</v>
       </c>
       <c r="H350" t="n">
         <v>29500</v>
@@ -10577,7 +10577,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G352" t="n">
-        <v>5.63560390472412</v>
+        <v>5.63560438156128</v>
       </c>
       <c r="H352" t="n">
         <v>16000</v>
@@ -10722,7 +10722,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G357" t="n">
-        <v>5.67501449584961</v>
+        <v>5.67501401901245</v>
       </c>
       <c r="H357" t="n">
         <v>2500</v>
@@ -10751,7 +10751,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G358" t="n">
-        <v>5.67501449584961</v>
+        <v>5.67501401901245</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G362" t="n">
-        <v>5.26121139526367</v>
+        <v>5.26121091842651</v>
       </c>
       <c r="H362" t="n">
         <v>19000</v>
@@ -11128,7 +11128,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G371" t="n">
-        <v>5.67501449584961</v>
+        <v>5.67501401901245</v>
       </c>
       <c r="H371" t="n">
         <v>3000</v>
@@ -11157,7 +11157,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>5.73412942886353</v>
+        <v>5.73412895202637</v>
       </c>
       <c r="H372" t="n">
         <v>4000</v>
@@ -11186,7 +11186,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>5.61589908599854</v>
+        <v>5.61589956283569</v>
       </c>
       <c r="H373" t="n">
         <v>6000</v>
@@ -11215,7 +11215,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.61589908599854</v>
+        <v>5.61589956283569</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G376" t="n">
-        <v>5.73412942886353</v>
+        <v>5.73412895202637</v>
       </c>
       <c r="H376" t="n">
         <v>3500</v>
@@ -11360,7 +11360,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>5.65530872344971</v>
+        <v>5.65530920028687</v>
       </c>
       <c r="H379" t="n">
         <v>3500</v>
@@ -11389,7 +11389,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G380" t="n">
-        <v>5.65530872344971</v>
+        <v>5.65530920028687</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G381" t="n">
-        <v>5.65530872344971</v>
+        <v>5.65530920028687</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>5.51737499237061</v>
+        <v>5.51737451553345</v>
       </c>
       <c r="H382" t="n">
         <v>2000</v>
@@ -11476,7 +11476,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>5.61589908599854</v>
+        <v>5.61589956283569</v>
       </c>
       <c r="H383" t="n">
         <v>14000</v>
@@ -11853,7 +11853,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>6.20704698562622</v>
+        <v>6.20704650878906</v>
       </c>
       <c r="H396" t="n">
         <v>5000</v>
@@ -12114,7 +12114,7 @@
         <v>6.5</v>
       </c>
       <c r="G405" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H405" t="n">
         <v>2500</v>
@@ -12143,7 +12143,7 @@
         <v>6.5</v>
       </c>
       <c r="G406" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H406" t="n">
         <v>2500</v>
@@ -12172,7 +12172,7 @@
         <v>6.5</v>
       </c>
       <c r="G407" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H407" t="n">
         <v>1500</v>
@@ -12201,7 +12201,7 @@
         <v>6.5</v>
       </c>
       <c r="G408" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12259,7 +12259,7 @@
         <v>6.5</v>
       </c>
       <c r="G410" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H410" t="n">
         <v>500</v>
@@ -12317,7 +12317,7 @@
         <v>6.5</v>
       </c>
       <c r="G412" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H412" t="n">
         <v>2000</v>
@@ -30216,6 +30216,64 @@
         <v>1000</v>
       </c>
       <c r="I1029" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1030" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1030" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="E1030" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="H1030" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I1030" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1031" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1031" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="D1031" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="H1031" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I1031" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -572,7 +572,7 @@
         <v>3.75</v>
       </c>
       <c r="G7" t="n">
-        <v>3.68279051780701</v>
+        <v>3.68279075622559</v>
       </c>
       <c r="H7" t="n">
         <v>5500</v>
@@ -659,7 +659,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G10" t="n">
-        <v>3.89884757995605</v>
+        <v>3.89884781837463</v>
       </c>
       <c r="H10" t="n">
         <v>36500</v>
@@ -717,7 +717,7 @@
         <v>3.8585000038147</v>
       </c>
       <c r="G12" t="n">
-        <v>3.78934621810913</v>
+        <v>3.78934597969055</v>
       </c>
       <c r="H12" t="n">
         <v>10000</v>
@@ -746,7 +746,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.71716356277466</v>
+        <v>3.71716380119324</v>
       </c>
       <c r="H13" t="n">
         <v>3000</v>
@@ -775,7 +775,7 @@
         <v>3.75</v>
       </c>
       <c r="G14" t="n">
-        <v>3.68279051780701</v>
+        <v>3.68279075622559</v>
       </c>
       <c r="H14" t="n">
         <v>500</v>
@@ -833,7 +833,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65332841873169</v>
+        <v>3.65332818031311</v>
       </c>
       <c r="H16" t="n">
         <v>9500</v>
@@ -862,7 +862,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G17" t="n">
-        <v>3.65332841873169</v>
+        <v>3.65332818031311</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>3.58458304405212</v>
+        <v>3.58458280563354</v>
       </c>
       <c r="H19" t="n">
         <v>4500</v>
@@ -1007,7 +1007,7 @@
         <v>3.75</v>
       </c>
       <c r="G22" t="n">
-        <v>3.68279051780701</v>
+        <v>3.68279075622559</v>
       </c>
       <c r="H22" t="n">
         <v>5500</v>
@@ -1036,7 +1036,7 @@
         <v>3.64949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>3.5840916633606</v>
+        <v>3.58409190177917</v>
       </c>
       <c r="H23" t="n">
         <v>1500</v>
@@ -1181,7 +1181,7 @@
         <v>3.50049996376038</v>
       </c>
       <c r="G28" t="n">
-        <v>3.43776226043701</v>
+        <v>3.43776249885559</v>
       </c>
       <c r="H28" t="n">
         <v>500</v>
@@ -1210,7 +1210,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>3.38816738128662</v>
+        <v>3.3881676197052</v>
       </c>
       <c r="H29" t="n">
         <v>3000</v>
@@ -1268,7 +1268,7 @@
         <v>3.28900003433228</v>
       </c>
       <c r="G31" t="n">
-        <v>3.23005270957947</v>
+        <v>3.23005294799805</v>
       </c>
       <c r="H31" t="n">
         <v>6000</v>
@@ -1355,7 +1355,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G34" t="n">
-        <v>2.98747992515564</v>
+        <v>2.98747968673706</v>
       </c>
       <c r="H34" t="n">
         <v>15500</v>
@@ -1413,7 +1413,7 @@
         <v>2.98699998855591</v>
       </c>
       <c r="G36" t="n">
-        <v>2.93346571922302</v>
+        <v>2.93346548080444</v>
       </c>
       <c r="H36" t="n">
         <v>14000</v>
@@ -1645,7 +1645,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.24085569381714</v>
+        <v>3.24085593223572</v>
       </c>
       <c r="H44" t="n">
         <v>51000</v>
@@ -1703,7 +1703,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>3.37834668159485</v>
+        <v>3.37834644317627</v>
       </c>
       <c r="H46" t="n">
         <v>37500</v>
@@ -1790,7 +1790,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G49" t="n">
-        <v>3.33857226371765</v>
+        <v>3.33857250213623</v>
       </c>
       <c r="H49" t="n">
         <v>12500</v>
@@ -2225,7 +2225,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.01497793197632</v>
+        <v>3.01497769355774</v>
       </c>
       <c r="H64" t="n">
         <v>2000</v>
@@ -2399,7 +2399,7 @@
         <v>3</v>
       </c>
       <c r="G70" t="n">
-        <v>2.94623255729675</v>
+        <v>2.94623231887817</v>
       </c>
       <c r="H70" t="n">
         <v>2500</v>
@@ -2428,7 +2428,7 @@
         <v>3</v>
       </c>
       <c r="G71" t="n">
-        <v>2.94623255729675</v>
+        <v>2.94623231887817</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>2.94623255729675</v>
+        <v>2.94623231887817</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.01497793197632</v>
+        <v>3.01497769355774</v>
       </c>
       <c r="H73" t="n">
         <v>500</v>
@@ -2515,7 +2515,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G74" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H74" t="n">
         <v>1000</v>
@@ -2718,7 +2718,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>2.9658739566803</v>
+        <v>2.96587419509888</v>
       </c>
       <c r="H81" t="n">
         <v>500</v>
@@ -2834,7 +2834,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H85" t="n">
         <v>1000</v>
@@ -2863,7 +2863,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G90" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H90" t="n">
         <v>1000</v>
@@ -3008,7 +3008,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G92" t="n">
-        <v>3.09354400634766</v>
+        <v>3.09354424476624</v>
       </c>
       <c r="H92" t="n">
         <v>1000</v>
@@ -3066,7 +3066,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.09354400634766</v>
+        <v>3.09354424476624</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>2.9658739566803</v>
+        <v>2.96587419509888</v>
       </c>
       <c r="H98" t="n">
         <v>8000</v>
@@ -3327,7 +3327,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>2.9658739566803</v>
+        <v>2.96587419509888</v>
       </c>
       <c r="H102" t="n">
         <v>4500</v>
@@ -3356,7 +3356,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G103" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H103" t="n">
         <v>1000</v>
@@ -3385,7 +3385,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G104" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G106" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>2.84802508354187</v>
+        <v>2.84802484512329</v>
       </c>
       <c r="H108" t="n">
         <v>10000</v>
@@ -3530,7 +3530,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>2.84802508354187</v>
+        <v>2.84802484512329</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G111" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H111" t="n">
         <v>500</v>
@@ -3617,7 +3617,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G112" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G113" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G114" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G115" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H115" t="n">
         <v>500</v>
@@ -4110,7 +4110,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>2.79892086982727</v>
+        <v>2.79892063140869</v>
       </c>
       <c r="H129" t="n">
         <v>8000</v>
@@ -4139,7 +4139,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>2.710533618927</v>
+        <v>2.71053385734558</v>
       </c>
       <c r="H130" t="n">
         <v>6500</v>
@@ -4168,7 +4168,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G131" t="n">
-        <v>2.74981689453125</v>
+        <v>2.74981713294983</v>
       </c>
       <c r="H131" t="n">
         <v>2000</v>
@@ -4197,7 +4197,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.74981689453125</v>
+        <v>2.74981713294983</v>
       </c>
       <c r="H132" t="n">
         <v>500</v>
@@ -4255,7 +4255,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.72035479545593</v>
+        <v>2.72035455703735</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.09354400634766</v>
+        <v>3.09354424476624</v>
       </c>
       <c r="H139" t="n">
         <v>6000</v>
@@ -4429,7 +4429,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.1328272819519</v>
+        <v>3.13282752037048</v>
       </c>
       <c r="H140" t="n">
         <v>1500</v>
@@ -4487,7 +4487,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G142" t="n">
-        <v>3.01497793197632</v>
+        <v>3.01497769355774</v>
       </c>
       <c r="H142" t="n">
         <v>4000</v>
@@ -4516,7 +4516,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G143" t="n">
-        <v>3.01497793197632</v>
+        <v>3.01497769355774</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>3.23103499412537</v>
+        <v>3.23103475570679</v>
       </c>
       <c r="H152" t="n">
         <v>54500</v>
@@ -4806,7 +4806,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>3.23103499412537</v>
+        <v>3.23103475570679</v>
       </c>
       <c r="H153" t="n">
         <v>13500</v>
@@ -4835,7 +4835,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>3.15246891975403</v>
+        <v>3.15246868133545</v>
       </c>
       <c r="H154" t="n">
         <v>5500</v>
@@ -4951,7 +4951,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G158" t="n">
-        <v>3.05426120758057</v>
+        <v>3.05426096916199</v>
       </c>
       <c r="H158" t="n">
         <v>3500</v>
@@ -4980,7 +4980,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G159" t="n">
-        <v>3.05426120758057</v>
+        <v>3.05426096916199</v>
       </c>
       <c r="H159" t="n">
         <v>500</v>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2" t="n">
-        <v>3.14264798164368</v>
+        <v>3.14264822006226</v>
       </c>
       <c r="H2" t="n">
         <v>26500</v>
@@ -746,7 +746,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.71716380119324</v>
+        <v>3.71716356277466</v>
       </c>
       <c r="H13" t="n">
         <v>3000</v>
@@ -804,7 +804,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.78099846839905</v>
+        <v>3.78099822998047</v>
       </c>
       <c r="H15" t="n">
         <v>2000</v>
@@ -833,7 +833,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65332818031311</v>
+        <v>3.65332841873169</v>
       </c>
       <c r="H16" t="n">
         <v>9500</v>
@@ -862,7 +862,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G17" t="n">
-        <v>3.65332818031311</v>
+        <v>3.65332841873169</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>3.58458280563354</v>
+        <v>3.58458304405212</v>
       </c>
       <c r="H19" t="n">
         <v>4500</v>
@@ -1036,7 +1036,7 @@
         <v>3.64949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>3.58409190177917</v>
+        <v>3.5840916633606</v>
       </c>
       <c r="H23" t="n">
         <v>1500</v>
@@ -1065,7 +1065,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G24" t="n">
-        <v>3.57476234436035</v>
+        <v>3.57476210594177</v>
       </c>
       <c r="H24" t="n">
         <v>5000</v>
@@ -1181,7 +1181,7 @@
         <v>3.50049996376038</v>
       </c>
       <c r="G28" t="n">
-        <v>3.43776249885559</v>
+        <v>3.43776226043701</v>
       </c>
       <c r="H28" t="n">
         <v>500</v>
@@ -1239,7 +1239,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>3.334153175354</v>
+        <v>3.33415293693542</v>
       </c>
       <c r="H30" t="n">
         <v>2000</v>
@@ -1355,7 +1355,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G34" t="n">
-        <v>2.98747968673706</v>
+        <v>2.98747992515564</v>
       </c>
       <c r="H34" t="n">
         <v>15500</v>
@@ -1645,7 +1645,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.24085593223572</v>
+        <v>3.24085569381714</v>
       </c>
       <c r="H44" t="n">
         <v>51000</v>
@@ -1703,7 +1703,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>3.37834644317627</v>
+        <v>3.37834668159485</v>
       </c>
       <c r="H46" t="n">
         <v>37500</v>
@@ -1819,7 +1819,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.28013896942139</v>
+        <v>3.28013873100281</v>
       </c>
       <c r="H50" t="n">
         <v>1000</v>
@@ -1848,7 +1848,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G51" t="n">
-        <v>3.28013896942139</v>
+        <v>3.28013873100281</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G52" t="n">
-        <v>3.28013896942139</v>
+        <v>3.28013873100281</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.29978013038635</v>
+        <v>3.29978036880493</v>
       </c>
       <c r="H53" t="n">
         <v>2500</v>
@@ -2196,7 +2196,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14264798164368</v>
+        <v>3.14264822006226</v>
       </c>
       <c r="H63" t="n">
         <v>2500</v>
@@ -2254,7 +2254,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G65" t="n">
-        <v>3.02479863166809</v>
+        <v>3.02479887008667</v>
       </c>
       <c r="H65" t="n">
         <v>1000</v>
@@ -2283,7 +2283,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>3.02479863166809</v>
+        <v>3.02479887008667</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>3.02479863166809</v>
+        <v>3.02479887008667</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G68" t="n">
-        <v>3.02479863166809</v>
+        <v>3.02479887008667</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>3.02479863166809</v>
+        <v>3.02479887008667</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H81" t="n">
         <v>500</v>
@@ -2747,7 +2747,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.06408190727234</v>
+        <v>3.06408166885376</v>
       </c>
       <c r="H82" t="n">
         <v>5000</v>
@@ -2776,7 +2776,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.06408190727234</v>
+        <v>3.06408166885376</v>
       </c>
       <c r="H83" t="n">
         <v>6500</v>
@@ -2834,7 +2834,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H85" t="n">
         <v>1000</v>
@@ -2863,7 +2863,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G90" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H90" t="n">
         <v>1000</v>
@@ -3008,7 +3008,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G92" t="n">
-        <v>3.09354424476624</v>
+        <v>3.09354448318481</v>
       </c>
       <c r="H92" t="n">
         <v>1000</v>
@@ -3066,7 +3066,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.09354424476624</v>
+        <v>3.09354448318481</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G94" t="n">
-        <v>3.06408190727234</v>
+        <v>3.06408166885376</v>
       </c>
       <c r="H94" t="n">
         <v>13500</v>
@@ -3211,7 +3211,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H98" t="n">
         <v>8000</v>
@@ -3240,7 +3240,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>3.00515699386597</v>
+        <v>3.00515723228455</v>
       </c>
       <c r="H99" t="n">
         <v>16000</v>
@@ -3269,7 +3269,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>3.00515699386597</v>
+        <v>3.00515723228455</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H102" t="n">
         <v>4500</v>
@@ -3588,7 +3588,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G111" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H111" t="n">
         <v>500</v>
@@ -3617,7 +3617,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G112" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G113" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G114" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G115" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H115" t="n">
         <v>500</v>
@@ -3965,7 +3965,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G124" t="n">
-        <v>2.86766624450684</v>
+        <v>2.86766648292542</v>
       </c>
       <c r="H124" t="n">
         <v>2000</v>
@@ -3994,7 +3994,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>2.86766624450684</v>
+        <v>2.86766648292542</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>2.86766624450684</v>
+        <v>2.86766648292542</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>2.86766624450684</v>
+        <v>2.86766648292542</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>2.79892063140869</v>
+        <v>2.79892086982727</v>
       </c>
       <c r="H129" t="n">
         <v>8000</v>
@@ -4371,7 +4371,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G138" t="n">
-        <v>3.10336518287659</v>
+        <v>3.10336494445801</v>
       </c>
       <c r="H138" t="n">
         <v>4500</v>
@@ -4400,7 +4400,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.09354424476624</v>
+        <v>3.09354448318481</v>
       </c>
       <c r="H139" t="n">
         <v>6000</v>
@@ -4429,7 +4429,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.13282752037048</v>
+        <v>3.1328272819519</v>
       </c>
       <c r="H140" t="n">
         <v>1500</v>
@@ -4458,7 +4458,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G141" t="n">
-        <v>3.02479863166809</v>
+        <v>3.02479887008667</v>
       </c>
       <c r="H141" t="n">
         <v>11000</v>
@@ -4545,7 +4545,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G144" t="n">
-        <v>2.99533653259277</v>
+        <v>2.99533629417419</v>
       </c>
       <c r="H144" t="n">
         <v>3000</v>
@@ -4661,7 +4661,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G148" t="n">
-        <v>3.07390260696411</v>
+        <v>3.07390284538269</v>
       </c>
       <c r="H148" t="n">
         <v>3000</v>
@@ -4777,7 +4777,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>3.23103475570679</v>
+        <v>3.23103499412537</v>
       </c>
       <c r="H152" t="n">
         <v>54500</v>
@@ -4806,7 +4806,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>3.23103475570679</v>
+        <v>3.23103499412537</v>
       </c>
       <c r="H153" t="n">
         <v>13500</v>
@@ -4864,7 +4864,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>3.14264798164368</v>
+        <v>3.14264822006226</v>
       </c>
       <c r="H155" t="n">
         <v>3500</v>
@@ -5067,7 +5067,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G162" t="n">
-        <v>3.06411361694336</v>
+        <v>3.06411337852478</v>
       </c>
       <c r="H162" t="n">
         <v>5500</v>
@@ -5096,7 +5096,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G163" t="n">
-        <v>3.06411361694336</v>
+        <v>3.06411337852478</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.33013010025024</v>
+        <v>3.33012986183167</v>
       </c>
       <c r="H164" t="n">
         <v>30000</v>
@@ -5154,7 +5154,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G165" t="n">
-        <v>3.33998227119446</v>
+        <v>3.33998250961304</v>
       </c>
       <c r="H165" t="n">
         <v>15500</v>
@@ -5270,7 +5270,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73408031463623</v>
+        <v>3.73408055305481</v>
       </c>
       <c r="H169" t="n">
         <v>17500</v>
@@ -5299,7 +5299,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G170" t="n">
-        <v>3.8227527141571</v>
+        <v>3.82275247573853</v>
       </c>
       <c r="H170" t="n">
         <v>16000</v>
@@ -5415,7 +5415,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G174" t="n">
-        <v>4.23655557632446</v>
+        <v>4.23655605316162</v>
       </c>
       <c r="H174" t="n">
         <v>14500</v>
@@ -5502,7 +5502,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G177" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H177" t="n">
         <v>3000</v>
@@ -5531,7 +5531,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H182" t="n">
         <v>4000</v>
@@ -5676,7 +5676,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>3.98039150238037</v>
+        <v>3.98039197921753</v>
       </c>
       <c r="H185" t="n">
         <v>1000</v>
@@ -5763,7 +5763,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>4.06906366348267</v>
+        <v>4.06906414031982</v>
       </c>
       <c r="H186" t="n">
         <v>3500</v>
@@ -6111,7 +6111,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G198" t="n">
-        <v>3.8227527141571</v>
+        <v>3.82275247573853</v>
       </c>
       <c r="H198" t="n">
         <v>5000</v>
@@ -6285,7 +6285,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H204" t="n">
         <v>2000</v>
@@ -6343,7 +6343,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>3.71437549591064</v>
+        <v>3.71437573432922</v>
       </c>
       <c r="H206" t="n">
         <v>1000</v>
@@ -6372,7 +6372,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G207" t="n">
-        <v>3.71437549591064</v>
+        <v>3.71437573432922</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G208" t="n">
-        <v>3.71437549591064</v>
+        <v>3.71437573432922</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>3.42865443229675</v>
+        <v>3.42865419387817</v>
       </c>
       <c r="H213" t="n">
         <v>2000</v>
@@ -6575,7 +6575,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G214" t="n">
-        <v>3.35968708992004</v>
+        <v>3.35968732833862</v>
       </c>
       <c r="H214" t="n">
         <v>4500</v>
@@ -6633,7 +6633,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G216" t="n">
-        <v>3.60599851608276</v>
+        <v>3.60599875450134</v>
       </c>
       <c r="H216" t="n">
         <v>13000</v>
@@ -6691,7 +6691,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>3.98039150238037</v>
+        <v>3.98039197921753</v>
       </c>
       <c r="H218" t="n">
         <v>16500</v>
@@ -6720,7 +6720,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G219" t="n">
-        <v>3.97053956985474</v>
+        <v>3.97053933143616</v>
       </c>
       <c r="H219" t="n">
         <v>8000</v>
@@ -6749,7 +6749,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>3.97053956985474</v>
+        <v>3.97053933143616</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G221" t="n">
-        <v>3.97053956985474</v>
+        <v>3.97053933143616</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06906366348267</v>
+        <v>4.06906414031982</v>
       </c>
       <c r="H222" t="n">
         <v>3500</v>
@@ -6836,7 +6836,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G223" t="n">
-        <v>4.06906366348267</v>
+        <v>4.06906414031982</v>
       </c>
       <c r="H223" t="n">
         <v>6000</v>
@@ -6894,7 +6894,7 @@
         <v>4.25</v>
       </c>
       <c r="G225" t="n">
-        <v>4.1872935295105</v>
+        <v>4.18729305267334</v>
       </c>
       <c r="H225" t="n">
         <v>4000</v>
@@ -6981,7 +6981,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G228" t="n">
-        <v>3.93112969398499</v>
+        <v>3.93112945556641</v>
       </c>
       <c r="H228" t="n">
         <v>10000</v>
@@ -7010,7 +7010,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G229" t="n">
-        <v>3.93112969398499</v>
+        <v>3.93112945556641</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G230" t="n">
-        <v>4.00009679794312</v>
+        <v>4.00009632110596</v>
       </c>
       <c r="H230" t="n">
         <v>500</v>
@@ -7068,7 +7068,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G231" t="n">
-        <v>4.00009679794312</v>
+        <v>4.00009632110596</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G232" t="n">
-        <v>4.00009679794312</v>
+        <v>4.00009632110596</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>3.98039150238037</v>
+        <v>3.98039197921753</v>
       </c>
       <c r="H236" t="n">
         <v>2000</v>
@@ -7242,7 +7242,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G237" t="n">
-        <v>3.98039150238037</v>
+        <v>3.98039197921753</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>3.98039150238037</v>
+        <v>3.98039197921753</v>
       </c>
       <c r="H241" t="n">
         <v>1500</v>
@@ -7416,7 +7416,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H243" t="n">
         <v>5000</v>
@@ -7880,7 +7880,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H259" t="n">
         <v>13500</v>
@@ -8054,7 +8054,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H265" t="n">
         <v>1000</v>
@@ -8257,7 +8257,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G272" t="n">
-        <v>3.53703141212463</v>
+        <v>3.53703117370605</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8286,7 +8286,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G273" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H273" t="n">
         <v>8000</v>
@@ -8315,7 +8315,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H274" t="n">
         <v>500</v>
@@ -8344,7 +8344,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G275" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H289" t="n">
         <v>4500</v>
@@ -8779,7 +8779,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G290" t="n">
-        <v>3.52717876434326</v>
+        <v>3.52717900276184</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G293" t="n">
-        <v>3.40894961357117</v>
+        <v>3.40894937515259</v>
       </c>
       <c r="H293" t="n">
         <v>13000</v>
@@ -8895,7 +8895,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G294" t="n">
-        <v>3.35968708992004</v>
+        <v>3.35968732833862</v>
       </c>
       <c r="H294" t="n">
         <v>7500</v>
@@ -9098,7 +9098,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G301" t="n">
-        <v>3.47791647911072</v>
+        <v>3.4779167175293</v>
       </c>
       <c r="H301" t="n">
         <v>500</v>
@@ -9127,7 +9127,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G302" t="n">
-        <v>3.47791647911072</v>
+        <v>3.4779167175293</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G304" t="n">
-        <v>3.53703141212463</v>
+        <v>3.53703117370605</v>
       </c>
       <c r="H304" t="n">
         <v>7000</v>
@@ -9214,7 +9214,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G305" t="n">
-        <v>3.66511344909668</v>
+        <v>3.6651132106781</v>
       </c>
       <c r="H305" t="n">
         <v>15000</v>
@@ -9359,7 +9359,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H310" t="n">
         <v>6000</v>
@@ -9417,7 +9417,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H312" t="n">
         <v>1000</v>
@@ -9446,7 +9446,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H313" t="n">
         <v>1500</v>
@@ -9475,7 +9475,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G314" t="n">
-        <v>3.98039150238037</v>
+        <v>3.98039197921753</v>
       </c>
       <c r="H314" t="n">
         <v>3000</v>
@@ -9620,7 +9620,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G319" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H319" t="n">
         <v>2000</v>
@@ -9649,7 +9649,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>3.9902446269989</v>
+        <v>3.99024438858032</v>
       </c>
       <c r="H321" t="n">
         <v>4000</v>
@@ -9997,7 +9997,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>4.07891654968262</v>
+        <v>4.07891607284546</v>
       </c>
       <c r="H332" t="n">
         <v>5000</v>
@@ -10055,7 +10055,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>4.06906366348267</v>
+        <v>4.06906414031982</v>
       </c>
       <c r="H334" t="n">
         <v>10000</v>
@@ -10113,7 +10113,7 @@
         <v>4.25</v>
       </c>
       <c r="G336" t="n">
-        <v>4.1872935295105</v>
+        <v>4.18729305267334</v>
       </c>
       <c r="H336" t="n">
         <v>6500</v>
@@ -10171,7 +10171,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>4.33508062362671</v>
+        <v>4.33508014678955</v>
       </c>
       <c r="H338" t="n">
         <v>1000</v>
@@ -10316,7 +10316,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G343" t="n">
-        <v>4.26611328125</v>
+        <v>4.26611280441284</v>
       </c>
       <c r="H343" t="n">
         <v>1000</v>
@@ -10345,7 +10345,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G344" t="n">
-        <v>4.26611328125</v>
+        <v>4.26611280441284</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>4.26611328125</v>
+        <v>4.26611280441284</v>
       </c>
       <c r="H345" t="n">
         <v>1000</v>
@@ -10519,7 +10519,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.77353858947754</v>
+        <v>5.7735390663147</v>
       </c>
       <c r="H350" t="n">
         <v>29500</v>
@@ -10577,7 +10577,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G352" t="n">
-        <v>5.63560438156128</v>
+        <v>5.63560390472412</v>
       </c>
       <c r="H352" t="n">
         <v>16000</v>
@@ -10722,7 +10722,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G357" t="n">
-        <v>5.67501401901245</v>
+        <v>5.67501449584961</v>
       </c>
       <c r="H357" t="n">
         <v>2500</v>
@@ -10751,7 +10751,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G358" t="n">
-        <v>5.67501401901245</v>
+        <v>5.67501449584961</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G362" t="n">
-        <v>5.26121091842651</v>
+        <v>5.26121139526367</v>
       </c>
       <c r="H362" t="n">
         <v>19000</v>
@@ -11128,7 +11128,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G371" t="n">
-        <v>5.67501401901245</v>
+        <v>5.67501449584961</v>
       </c>
       <c r="H371" t="n">
         <v>3000</v>
@@ -11157,7 +11157,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>5.73412895202637</v>
+        <v>5.73412942886353</v>
       </c>
       <c r="H372" t="n">
         <v>4000</v>
@@ -11186,7 +11186,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>5.61589956283569</v>
+        <v>5.61589908599854</v>
       </c>
       <c r="H373" t="n">
         <v>6000</v>
@@ -11215,7 +11215,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.61589956283569</v>
+        <v>5.61589908599854</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G376" t="n">
-        <v>5.73412895202637</v>
+        <v>5.73412942886353</v>
       </c>
       <c r="H376" t="n">
         <v>3500</v>
@@ -11360,7 +11360,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>5.65530920028687</v>
+        <v>5.65530872344971</v>
       </c>
       <c r="H379" t="n">
         <v>3500</v>
@@ -11389,7 +11389,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G380" t="n">
-        <v>5.65530920028687</v>
+        <v>5.65530872344971</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G381" t="n">
-        <v>5.65530920028687</v>
+        <v>5.65530872344971</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>5.51737451553345</v>
+        <v>5.51737499237061</v>
       </c>
       <c r="H382" t="n">
         <v>2000</v>
@@ -11476,7 +11476,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>5.61589956283569</v>
+        <v>5.61589908599854</v>
       </c>
       <c r="H383" t="n">
         <v>14000</v>
@@ -11853,7 +11853,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>6.20704650878906</v>
+        <v>6.20704698562622</v>
       </c>
       <c r="H396" t="n">
         <v>5000</v>
@@ -12114,7 +12114,7 @@
         <v>6.5</v>
       </c>
       <c r="G405" t="n">
-        <v>6.4040961265564</v>
+        <v>6.40409564971924</v>
       </c>
       <c r="H405" t="n">
         <v>2500</v>
@@ -12143,7 +12143,7 @@
         <v>6.5</v>
       </c>
       <c r="G406" t="n">
-        <v>6.4040961265564</v>
+        <v>6.40409564971924</v>
       </c>
       <c r="H406" t="n">
         <v>2500</v>
@@ -12172,7 +12172,7 @@
         <v>6.5</v>
       </c>
       <c r="G407" t="n">
-        <v>6.4040961265564</v>
+        <v>6.40409564971924</v>
       </c>
       <c r="H407" t="n">
         <v>1500</v>
@@ -12201,7 +12201,7 @@
         <v>6.5</v>
       </c>
       <c r="G408" t="n">
-        <v>6.4040961265564</v>
+        <v>6.40409564971924</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12259,7 +12259,7 @@
         <v>6.5</v>
       </c>
       <c r="G410" t="n">
-        <v>6.4040961265564</v>
+        <v>6.40409564971924</v>
       </c>
       <c r="H410" t="n">
         <v>500</v>
@@ -12317,7 +12317,7 @@
         <v>6.5</v>
       </c>
       <c r="G412" t="n">
-        <v>6.4040961265564</v>
+        <v>6.40409564971924</v>
       </c>
       <c r="H412" t="n">
         <v>2000</v>
@@ -30274,6 +30274,64 @@
         <v>1500</v>
       </c>
       <c r="I1031" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1032" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1032" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="D1032" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="H1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1032" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1033" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1033" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="D1033" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="E1033" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1033" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1033" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2" t="n">
-        <v>3.14264822006226</v>
+        <v>3.14264798164368</v>
       </c>
       <c r="H2" t="n">
         <v>26500</v>
@@ -746,7 +746,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.71716356277466</v>
+        <v>3.71716380119324</v>
       </c>
       <c r="H13" t="n">
         <v>3000</v>
@@ -804,7 +804,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G15" t="n">
-        <v>3.78099822998047</v>
+        <v>3.78099846839905</v>
       </c>
       <c r="H15" t="n">
         <v>2000</v>
@@ -833,7 +833,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65332841873169</v>
+        <v>3.65332818031311</v>
       </c>
       <c r="H16" t="n">
         <v>9500</v>
@@ -862,7 +862,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G17" t="n">
-        <v>3.65332841873169</v>
+        <v>3.65332818031311</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>3.58458304405212</v>
+        <v>3.58458280563354</v>
       </c>
       <c r="H19" t="n">
         <v>4500</v>
@@ -1036,7 +1036,7 @@
         <v>3.64949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>3.5840916633606</v>
+        <v>3.58409190177917</v>
       </c>
       <c r="H23" t="n">
         <v>1500</v>
@@ -1065,7 +1065,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G24" t="n">
-        <v>3.57476210594177</v>
+        <v>3.57476234436035</v>
       </c>
       <c r="H24" t="n">
         <v>5000</v>
@@ -1181,7 +1181,7 @@
         <v>3.50049996376038</v>
       </c>
       <c r="G28" t="n">
-        <v>3.43776226043701</v>
+        <v>3.43776249885559</v>
       </c>
       <c r="H28" t="n">
         <v>500</v>
@@ -1239,7 +1239,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>3.33415293693542</v>
+        <v>3.334153175354</v>
       </c>
       <c r="H30" t="n">
         <v>2000</v>
@@ -1355,7 +1355,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G34" t="n">
-        <v>2.98747992515564</v>
+        <v>2.98747968673706</v>
       </c>
       <c r="H34" t="n">
         <v>15500</v>
@@ -1645,7 +1645,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.24085569381714</v>
+        <v>3.24085593223572</v>
       </c>
       <c r="H44" t="n">
         <v>51000</v>
@@ -1703,7 +1703,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>3.37834668159485</v>
+        <v>3.37834644317627</v>
       </c>
       <c r="H46" t="n">
         <v>37500</v>
@@ -1819,7 +1819,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.28013873100281</v>
+        <v>3.28013896942139</v>
       </c>
       <c r="H50" t="n">
         <v>1000</v>
@@ -1848,7 +1848,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G51" t="n">
-        <v>3.28013873100281</v>
+        <v>3.28013896942139</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G52" t="n">
-        <v>3.28013873100281</v>
+        <v>3.28013896942139</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.29978036880493</v>
+        <v>3.29978013038635</v>
       </c>
       <c r="H53" t="n">
         <v>2500</v>
@@ -2196,7 +2196,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14264822006226</v>
+        <v>3.14264798164368</v>
       </c>
       <c r="H63" t="n">
         <v>2500</v>
@@ -2254,7 +2254,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G65" t="n">
-        <v>3.02479887008667</v>
+        <v>3.02479863166809</v>
       </c>
       <c r="H65" t="n">
         <v>1000</v>
@@ -2283,7 +2283,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>3.02479887008667</v>
+        <v>3.02479863166809</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>3.02479887008667</v>
+        <v>3.02479863166809</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G68" t="n">
-        <v>3.02479887008667</v>
+        <v>3.02479863166809</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G69" t="n">
-        <v>3.02479887008667</v>
+        <v>3.02479863166809</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>2.9658739566803</v>
+        <v>2.96587419509888</v>
       </c>
       <c r="H81" t="n">
         <v>500</v>
@@ -2747,7 +2747,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G82" t="n">
-        <v>3.06408166885376</v>
+        <v>3.06408190727234</v>
       </c>
       <c r="H82" t="n">
         <v>5000</v>
@@ -2776,7 +2776,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G83" t="n">
-        <v>3.06408166885376</v>
+        <v>3.06408190727234</v>
       </c>
       <c r="H83" t="n">
         <v>6500</v>
@@ -2834,7 +2834,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H85" t="n">
         <v>1000</v>
@@ -2863,7 +2863,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G90" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H90" t="n">
         <v>1000</v>
@@ -3008,7 +3008,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G92" t="n">
-        <v>3.09354448318481</v>
+        <v>3.09354424476624</v>
       </c>
       <c r="H92" t="n">
         <v>1000</v>
@@ -3066,7 +3066,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.09354448318481</v>
+        <v>3.09354424476624</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G94" t="n">
-        <v>3.06408166885376</v>
+        <v>3.06408190727234</v>
       </c>
       <c r="H94" t="n">
         <v>13500</v>
@@ -3211,7 +3211,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>2.9658739566803</v>
+        <v>2.96587419509888</v>
       </c>
       <c r="H98" t="n">
         <v>8000</v>
@@ -3240,7 +3240,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G99" t="n">
-        <v>3.00515723228455</v>
+        <v>3.00515699386597</v>
       </c>
       <c r="H99" t="n">
         <v>16000</v>
@@ -3269,7 +3269,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G100" t="n">
-        <v>3.00515723228455</v>
+        <v>3.00515699386597</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>2.9658739566803</v>
+        <v>2.96587419509888</v>
       </c>
       <c r="H102" t="n">
         <v>4500</v>
@@ -3588,7 +3588,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G111" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H111" t="n">
         <v>500</v>
@@ -3617,7 +3617,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G112" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G113" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G114" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G115" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H115" t="n">
         <v>500</v>
@@ -3965,7 +3965,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G124" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H124" t="n">
         <v>2000</v>
@@ -3994,7 +3994,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G125" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G127" t="n">
-        <v>2.86766648292542</v>
+        <v>2.86766624450684</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>2.79892086982727</v>
+        <v>2.79892063140869</v>
       </c>
       <c r="H129" t="n">
         <v>8000</v>
@@ -4371,7 +4371,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G138" t="n">
-        <v>3.10336494445801</v>
+        <v>3.10336518287659</v>
       </c>
       <c r="H138" t="n">
         <v>4500</v>
@@ -4400,7 +4400,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.09354448318481</v>
+        <v>3.09354424476624</v>
       </c>
       <c r="H139" t="n">
         <v>6000</v>
@@ -4429,7 +4429,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.1328272819519</v>
+        <v>3.13282752037048</v>
       </c>
       <c r="H140" t="n">
         <v>1500</v>
@@ -4458,7 +4458,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G141" t="n">
-        <v>3.02479887008667</v>
+        <v>3.02479863166809</v>
       </c>
       <c r="H141" t="n">
         <v>11000</v>
@@ -4545,7 +4545,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G144" t="n">
-        <v>2.99533629417419</v>
+        <v>2.99533653259277</v>
       </c>
       <c r="H144" t="n">
         <v>3000</v>
@@ -4661,7 +4661,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G148" t="n">
-        <v>3.07390284538269</v>
+        <v>3.07390260696411</v>
       </c>
       <c r="H148" t="n">
         <v>3000</v>
@@ -4777,7 +4777,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>3.23103499412537</v>
+        <v>3.23103475570679</v>
       </c>
       <c r="H152" t="n">
         <v>54500</v>
@@ -4806,7 +4806,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>3.23103499412537</v>
+        <v>3.23103475570679</v>
       </c>
       <c r="H153" t="n">
         <v>13500</v>
@@ -4864,7 +4864,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>3.14264822006226</v>
+        <v>3.14264798164368</v>
       </c>
       <c r="H155" t="n">
         <v>3500</v>
@@ -5067,7 +5067,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G162" t="n">
-        <v>3.06411337852478</v>
+        <v>3.06411361694336</v>
       </c>
       <c r="H162" t="n">
         <v>5500</v>
@@ -5096,7 +5096,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G163" t="n">
-        <v>3.06411337852478</v>
+        <v>3.06411361694336</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G164" t="n">
-        <v>3.33012986183167</v>
+        <v>3.33013010025024</v>
       </c>
       <c r="H164" t="n">
         <v>30000</v>
@@ -5154,7 +5154,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G165" t="n">
-        <v>3.33998250961304</v>
+        <v>3.33998227119446</v>
       </c>
       <c r="H165" t="n">
         <v>15500</v>
@@ -5270,7 +5270,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G169" t="n">
-        <v>3.73408055305481</v>
+        <v>3.73408031463623</v>
       </c>
       <c r="H169" t="n">
         <v>17500</v>
@@ -5299,7 +5299,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G170" t="n">
-        <v>3.82275247573853</v>
+        <v>3.8227527141571</v>
       </c>
       <c r="H170" t="n">
         <v>16000</v>
@@ -5415,7 +5415,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G174" t="n">
-        <v>4.23655605316162</v>
+        <v>4.23655557632446</v>
       </c>
       <c r="H174" t="n">
         <v>14500</v>
@@ -5502,7 +5502,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G177" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H177" t="n">
         <v>3000</v>
@@ -5531,7 +5531,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G182" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H182" t="n">
         <v>4000</v>
@@ -5676,7 +5676,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G185" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H185" t="n">
         <v>1000</v>
@@ -5763,7 +5763,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H186" t="n">
         <v>3500</v>
@@ -6111,7 +6111,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G198" t="n">
-        <v>3.82275247573853</v>
+        <v>3.8227527141571</v>
       </c>
       <c r="H198" t="n">
         <v>5000</v>
@@ -6285,7 +6285,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G204" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H204" t="n">
         <v>2000</v>
@@ -6343,7 +6343,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G206" t="n">
-        <v>3.71437573432922</v>
+        <v>3.71437549591064</v>
       </c>
       <c r="H206" t="n">
         <v>1000</v>
@@ -6372,7 +6372,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G207" t="n">
-        <v>3.71437573432922</v>
+        <v>3.71437549591064</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G208" t="n">
-        <v>3.71437573432922</v>
+        <v>3.71437549591064</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>3.42865419387817</v>
+        <v>3.42865443229675</v>
       </c>
       <c r="H213" t="n">
         <v>2000</v>
@@ -6575,7 +6575,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G214" t="n">
-        <v>3.35968732833862</v>
+        <v>3.35968708992004</v>
       </c>
       <c r="H214" t="n">
         <v>4500</v>
@@ -6633,7 +6633,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G216" t="n">
-        <v>3.60599875450134</v>
+        <v>3.60599851608276</v>
       </c>
       <c r="H216" t="n">
         <v>13000</v>
@@ -6691,7 +6691,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G218" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H218" t="n">
         <v>16500</v>
@@ -6720,7 +6720,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G219" t="n">
-        <v>3.97053933143616</v>
+        <v>3.97053956985474</v>
       </c>
       <c r="H219" t="n">
         <v>8000</v>
@@ -6749,7 +6749,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>3.97053933143616</v>
+        <v>3.97053956985474</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G221" t="n">
-        <v>3.97053933143616</v>
+        <v>3.97053956985474</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G222" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H222" t="n">
         <v>3500</v>
@@ -6836,7 +6836,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G223" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H223" t="n">
         <v>6000</v>
@@ -6894,7 +6894,7 @@
         <v>4.25</v>
       </c>
       <c r="G225" t="n">
-        <v>4.18729305267334</v>
+        <v>4.1872935295105</v>
       </c>
       <c r="H225" t="n">
         <v>4000</v>
@@ -6981,7 +6981,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G228" t="n">
-        <v>3.93112945556641</v>
+        <v>3.93112969398499</v>
       </c>
       <c r="H228" t="n">
         <v>10000</v>
@@ -7010,7 +7010,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G229" t="n">
-        <v>3.93112945556641</v>
+        <v>3.93112969398499</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G230" t="n">
-        <v>4.00009632110596</v>
+        <v>4.00009679794312</v>
       </c>
       <c r="H230" t="n">
         <v>500</v>
@@ -7068,7 +7068,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G231" t="n">
-        <v>4.00009632110596</v>
+        <v>4.00009679794312</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G232" t="n">
-        <v>4.00009632110596</v>
+        <v>4.00009679794312</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H236" t="n">
         <v>2000</v>
@@ -7242,7 +7242,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G237" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G241" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H241" t="n">
         <v>1500</v>
@@ -7416,7 +7416,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G243" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H243" t="n">
         <v>5000</v>
@@ -7880,7 +7880,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G259" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H259" t="n">
         <v>13500</v>
@@ -8054,7 +8054,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G265" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H265" t="n">
         <v>1000</v>
@@ -8257,7 +8257,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G272" t="n">
-        <v>3.53703117370605</v>
+        <v>3.53703141212463</v>
       </c>
       <c r="H272" t="n">
         <v>1500</v>
@@ -8286,7 +8286,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G273" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H273" t="n">
         <v>8000</v>
@@ -8315,7 +8315,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H274" t="n">
         <v>500</v>
@@ -8344,7 +8344,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G275" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H289" t="n">
         <v>4500</v>
@@ -8779,7 +8779,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G290" t="n">
-        <v>3.52717900276184</v>
+        <v>3.52717876434326</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G293" t="n">
-        <v>3.40894937515259</v>
+        <v>3.40894961357117</v>
       </c>
       <c r="H293" t="n">
         <v>13000</v>
@@ -8895,7 +8895,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G294" t="n">
-        <v>3.35968732833862</v>
+        <v>3.35968708992004</v>
       </c>
       <c r="H294" t="n">
         <v>7500</v>
@@ -9098,7 +9098,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G301" t="n">
-        <v>3.4779167175293</v>
+        <v>3.47791647911072</v>
       </c>
       <c r="H301" t="n">
         <v>500</v>
@@ -9127,7 +9127,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G302" t="n">
-        <v>3.4779167175293</v>
+        <v>3.47791647911072</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G304" t="n">
-        <v>3.53703117370605</v>
+        <v>3.53703141212463</v>
       </c>
       <c r="H304" t="n">
         <v>7000</v>
@@ -9214,7 +9214,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G305" t="n">
-        <v>3.6651132106781</v>
+        <v>3.66511344909668</v>
       </c>
       <c r="H305" t="n">
         <v>15000</v>
@@ -9359,7 +9359,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H310" t="n">
         <v>6000</v>
@@ -9417,7 +9417,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G312" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H312" t="n">
         <v>1000</v>
@@ -9446,7 +9446,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H313" t="n">
         <v>1500</v>
@@ -9475,7 +9475,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G314" t="n">
-        <v>3.98039197921753</v>
+        <v>3.98039150238037</v>
       </c>
       <c r="H314" t="n">
         <v>3000</v>
@@ -9620,7 +9620,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G319" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H319" t="n">
         <v>2000</v>
@@ -9649,7 +9649,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>3.99024438858032</v>
+        <v>3.9902446269989</v>
       </c>
       <c r="H321" t="n">
         <v>4000</v>
@@ -9997,7 +9997,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G332" t="n">
-        <v>4.07891607284546</v>
+        <v>4.07891654968262</v>
       </c>
       <c r="H332" t="n">
         <v>5000</v>
@@ -10055,7 +10055,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>4.06906414031982</v>
+        <v>4.06906366348267</v>
       </c>
       <c r="H334" t="n">
         <v>10000</v>
@@ -10113,7 +10113,7 @@
         <v>4.25</v>
       </c>
       <c r="G336" t="n">
-        <v>4.18729305267334</v>
+        <v>4.1872935295105</v>
       </c>
       <c r="H336" t="n">
         <v>6500</v>
@@ -10171,7 +10171,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>4.33508014678955</v>
+        <v>4.33508062362671</v>
       </c>
       <c r="H338" t="n">
         <v>1000</v>
@@ -10316,7 +10316,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G343" t="n">
-        <v>4.26611280441284</v>
+        <v>4.26611328125</v>
       </c>
       <c r="H343" t="n">
         <v>1000</v>
@@ -10345,7 +10345,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G344" t="n">
-        <v>4.26611280441284</v>
+        <v>4.26611328125</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>4.26611280441284</v>
+        <v>4.26611328125</v>
       </c>
       <c r="H345" t="n">
         <v>1000</v>
@@ -10519,7 +10519,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G350" t="n">
-        <v>5.7735390663147</v>
+        <v>5.77353858947754</v>
       </c>
       <c r="H350" t="n">
         <v>29500</v>
@@ -10577,7 +10577,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G352" t="n">
-        <v>5.63560390472412</v>
+        <v>5.63560438156128</v>
       </c>
       <c r="H352" t="n">
         <v>16000</v>
@@ -10722,7 +10722,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G357" t="n">
-        <v>5.67501449584961</v>
+        <v>5.67501401901245</v>
       </c>
       <c r="H357" t="n">
         <v>2500</v>
@@ -10751,7 +10751,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G358" t="n">
-        <v>5.67501449584961</v>
+        <v>5.67501401901245</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G362" t="n">
-        <v>5.26121139526367</v>
+        <v>5.26121091842651</v>
       </c>
       <c r="H362" t="n">
         <v>19000</v>
@@ -11128,7 +11128,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G371" t="n">
-        <v>5.67501449584961</v>
+        <v>5.67501401901245</v>
       </c>
       <c r="H371" t="n">
         <v>3000</v>
@@ -11157,7 +11157,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G372" t="n">
-        <v>5.73412942886353</v>
+        <v>5.73412895202637</v>
       </c>
       <c r="H372" t="n">
         <v>4000</v>
@@ -11186,7 +11186,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G373" t="n">
-        <v>5.61589908599854</v>
+        <v>5.61589956283569</v>
       </c>
       <c r="H373" t="n">
         <v>6000</v>
@@ -11215,7 +11215,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.61589908599854</v>
+        <v>5.61589956283569</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G376" t="n">
-        <v>5.73412942886353</v>
+        <v>5.73412895202637</v>
       </c>
       <c r="H376" t="n">
         <v>3500</v>
@@ -11360,7 +11360,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G379" t="n">
-        <v>5.65530872344971</v>
+        <v>5.65530920028687</v>
       </c>
       <c r="H379" t="n">
         <v>3500</v>
@@ -11389,7 +11389,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G380" t="n">
-        <v>5.65530872344971</v>
+        <v>5.65530920028687</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G381" t="n">
-        <v>5.65530872344971</v>
+        <v>5.65530920028687</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>5.51737499237061</v>
+        <v>5.51737451553345</v>
       </c>
       <c r="H382" t="n">
         <v>2000</v>
@@ -11476,7 +11476,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>5.61589908599854</v>
+        <v>5.61589956283569</v>
       </c>
       <c r="H383" t="n">
         <v>14000</v>
@@ -11853,7 +11853,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G396" t="n">
-        <v>6.20704698562622</v>
+        <v>6.20704650878906</v>
       </c>
       <c r="H396" t="n">
         <v>5000</v>
@@ -12114,7 +12114,7 @@
         <v>6.5</v>
       </c>
       <c r="G405" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H405" t="n">
         <v>2500</v>
@@ -12143,7 +12143,7 @@
         <v>6.5</v>
       </c>
       <c r="G406" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H406" t="n">
         <v>2500</v>
@@ -12172,7 +12172,7 @@
         <v>6.5</v>
       </c>
       <c r="G407" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H407" t="n">
         <v>1500</v>
@@ -12201,7 +12201,7 @@
         <v>6.5</v>
       </c>
       <c r="G408" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12259,7 +12259,7 @@
         <v>6.5</v>
       </c>
       <c r="G410" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H410" t="n">
         <v>500</v>
@@ -12317,7 +12317,7 @@
         <v>6.5</v>
       </c>
       <c r="G412" t="n">
-        <v>6.40409564971924</v>
+        <v>6.4040961265564</v>
       </c>
       <c r="H412" t="n">
         <v>2000</v>
@@ -30332,6 +30332,35 @@
         <v>3000</v>
       </c>
       <c r="I1033" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1034" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1034" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1034" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1034" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1034" t="n">
+        <v>500</v>
+      </c>
+      <c r="I1034" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -572,7 +572,7 @@
         <v>3.75</v>
       </c>
       <c r="G7" t="n">
-        <v>3.68279075622559</v>
+        <v>3.68279051780701</v>
       </c>
       <c r="H7" t="n">
         <v>5500</v>
@@ -659,7 +659,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G10" t="n">
-        <v>3.89884781837463</v>
+        <v>3.89884757995605</v>
       </c>
       <c r="H10" t="n">
         <v>36500</v>
@@ -717,7 +717,7 @@
         <v>3.8585000038147</v>
       </c>
       <c r="G12" t="n">
-        <v>3.78934597969055</v>
+        <v>3.78934621810913</v>
       </c>
       <c r="H12" t="n">
         <v>10000</v>
@@ -746,7 +746,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.71716380119324</v>
+        <v>3.71716356277466</v>
       </c>
       <c r="H13" t="n">
         <v>3000</v>
@@ -775,7 +775,7 @@
         <v>3.75</v>
       </c>
       <c r="G14" t="n">
-        <v>3.68279075622559</v>
+        <v>3.68279051780701</v>
       </c>
       <c r="H14" t="n">
         <v>500</v>
@@ -833,7 +833,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65332818031311</v>
+        <v>3.65332841873169</v>
       </c>
       <c r="H16" t="n">
         <v>9500</v>
@@ -862,7 +862,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G17" t="n">
-        <v>3.65332818031311</v>
+        <v>3.65332841873169</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>3.58458280563354</v>
+        <v>3.58458304405212</v>
       </c>
       <c r="H19" t="n">
         <v>4500</v>
@@ -1007,7 +1007,7 @@
         <v>3.75</v>
       </c>
       <c r="G22" t="n">
-        <v>3.68279075622559</v>
+        <v>3.68279051780701</v>
       </c>
       <c r="H22" t="n">
         <v>5500</v>
@@ -1036,7 +1036,7 @@
         <v>3.64949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>3.58409190177917</v>
+        <v>3.5840916633606</v>
       </c>
       <c r="H23" t="n">
         <v>1500</v>
@@ -1181,7 +1181,7 @@
         <v>3.50049996376038</v>
       </c>
       <c r="G28" t="n">
-        <v>3.43776249885559</v>
+        <v>3.43776226043701</v>
       </c>
       <c r="H28" t="n">
         <v>500</v>
@@ -1210,7 +1210,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>3.3881676197052</v>
+        <v>3.38816738128662</v>
       </c>
       <c r="H29" t="n">
         <v>3000</v>
@@ -1268,7 +1268,7 @@
         <v>3.28900003433228</v>
       </c>
       <c r="G31" t="n">
-        <v>3.23005294799805</v>
+        <v>3.23005270957947</v>
       </c>
       <c r="H31" t="n">
         <v>6000</v>
@@ -1355,7 +1355,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G34" t="n">
-        <v>2.98747968673706</v>
+        <v>2.98747992515564</v>
       </c>
       <c r="H34" t="n">
         <v>15500</v>
@@ -1413,7 +1413,7 @@
         <v>2.98699998855591</v>
       </c>
       <c r="G36" t="n">
-        <v>2.93346548080444</v>
+        <v>2.93346571922302</v>
       </c>
       <c r="H36" t="n">
         <v>14000</v>
@@ -1645,7 +1645,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.24085593223572</v>
+        <v>3.24085569381714</v>
       </c>
       <c r="H44" t="n">
         <v>51000</v>
@@ -1703,7 +1703,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>3.37834644317627</v>
+        <v>3.37834668159485</v>
       </c>
       <c r="H46" t="n">
         <v>37500</v>
@@ -1790,7 +1790,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G49" t="n">
-        <v>3.33857250213623</v>
+        <v>3.33857226371765</v>
       </c>
       <c r="H49" t="n">
         <v>12500</v>
@@ -2225,7 +2225,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.01497769355774</v>
+        <v>3.01497793197632</v>
       </c>
       <c r="H64" t="n">
         <v>2000</v>
@@ -2399,7 +2399,7 @@
         <v>3</v>
       </c>
       <c r="G70" t="n">
-        <v>2.94623231887817</v>
+        <v>2.94623255729675</v>
       </c>
       <c r="H70" t="n">
         <v>2500</v>
@@ -2428,7 +2428,7 @@
         <v>3</v>
       </c>
       <c r="G71" t="n">
-        <v>2.94623231887817</v>
+        <v>2.94623255729675</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>2.94623231887817</v>
+        <v>2.94623255729675</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.01497769355774</v>
+        <v>3.01497793197632</v>
       </c>
       <c r="H73" t="n">
         <v>500</v>
@@ -2515,7 +2515,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G74" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H74" t="n">
         <v>1000</v>
@@ -2718,7 +2718,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H81" t="n">
         <v>500</v>
@@ -2834,7 +2834,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H85" t="n">
         <v>1000</v>
@@ -2863,7 +2863,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G90" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H90" t="n">
         <v>1000</v>
@@ -3008,7 +3008,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G92" t="n">
-        <v>3.09354424476624</v>
+        <v>3.09354400634766</v>
       </c>
       <c r="H92" t="n">
         <v>1000</v>
@@ -3066,7 +3066,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.09354424476624</v>
+        <v>3.09354400634766</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H98" t="n">
         <v>8000</v>
@@ -3327,7 +3327,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H102" t="n">
         <v>4500</v>
@@ -3356,7 +3356,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G103" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H103" t="n">
         <v>1000</v>
@@ -3385,7 +3385,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G104" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G106" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>2.84802484512329</v>
+        <v>2.84802508354187</v>
       </c>
       <c r="H108" t="n">
         <v>10000</v>
@@ -3530,7 +3530,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>2.84802484512329</v>
+        <v>2.84802508354187</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G111" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H111" t="n">
         <v>500</v>
@@ -3617,7 +3617,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G112" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G113" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G114" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G115" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H115" t="n">
         <v>500</v>
@@ -4110,7 +4110,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>2.79892063140869</v>
+        <v>2.79892086982727</v>
       </c>
       <c r="H129" t="n">
         <v>8000</v>
@@ -4139,7 +4139,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>2.71053385734558</v>
+        <v>2.710533618927</v>
       </c>
       <c r="H130" t="n">
         <v>6500</v>
@@ -4168,7 +4168,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G131" t="n">
-        <v>2.74981713294983</v>
+        <v>2.74981689453125</v>
       </c>
       <c r="H131" t="n">
         <v>2000</v>
@@ -4197,7 +4197,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.74981713294983</v>
+        <v>2.74981689453125</v>
       </c>
       <c r="H132" t="n">
         <v>500</v>
@@ -4255,7 +4255,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.72035455703735</v>
+        <v>2.72035479545593</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.09354424476624</v>
+        <v>3.09354400634766</v>
       </c>
       <c r="H139" t="n">
         <v>6000</v>
@@ -4429,7 +4429,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.13282752037048</v>
+        <v>3.1328272819519</v>
       </c>
       <c r="H140" t="n">
         <v>1500</v>
@@ -4487,7 +4487,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G142" t="n">
-        <v>3.01497769355774</v>
+        <v>3.01497793197632</v>
       </c>
       <c r="H142" t="n">
         <v>4000</v>
@@ -4516,7 +4516,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G143" t="n">
-        <v>3.01497769355774</v>
+        <v>3.01497793197632</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>3.23103475570679</v>
+        <v>3.23103499412537</v>
       </c>
       <c r="H152" t="n">
         <v>54500</v>
@@ -4806,7 +4806,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>3.23103475570679</v>
+        <v>3.23103499412537</v>
       </c>
       <c r="H153" t="n">
         <v>13500</v>
@@ -4835,7 +4835,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>3.15246868133545</v>
+        <v>3.15246891975403</v>
       </c>
       <c r="H154" t="n">
         <v>5500</v>
@@ -4951,7 +4951,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G158" t="n">
-        <v>3.05426096916199</v>
+        <v>3.05426120758057</v>
       </c>
       <c r="H158" t="n">
         <v>3500</v>
@@ -4980,7 +4980,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G159" t="n">
-        <v>3.05426096916199</v>
+        <v>3.05426120758057</v>
       </c>
       <c r="H159" t="n">
         <v>500</v>
@@ -30361,6 +30361,35 @@
         <v>500</v>
       </c>
       <c r="I1034" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1035" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1035" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1035" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1035" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1035" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I1035" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2" t="n">
-        <v>3.14264798164368</v>
+        <v>3.14264822006226</v>
       </c>
       <c r="H2" t="n">
         <v>26500</v>
@@ -485,7 +485,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G4" t="n">
-        <v>3.67296981811523</v>
+        <v>3.67297005653381</v>
       </c>
       <c r="H4" t="n">
         <v>18000</v>
@@ -572,7 +572,7 @@
         <v>3.75</v>
       </c>
       <c r="G7" t="n">
-        <v>3.68279051780701</v>
+        <v>3.68279075622559</v>
       </c>
       <c r="H7" t="n">
         <v>5500</v>
@@ -659,7 +659,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G10" t="n">
-        <v>3.89884757995605</v>
+        <v>3.89884781837463</v>
       </c>
       <c r="H10" t="n">
         <v>36500</v>
@@ -775,7 +775,7 @@
         <v>3.75</v>
       </c>
       <c r="G14" t="n">
-        <v>3.68279051780701</v>
+        <v>3.68279075622559</v>
       </c>
       <c r="H14" t="n">
         <v>500</v>
@@ -891,7 +891,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>3.63368701934814</v>
+        <v>3.63368678092957</v>
       </c>
       <c r="H18" t="n">
         <v>2500</v>
@@ -1007,7 +1007,7 @@
         <v>3.75</v>
       </c>
       <c r="G22" t="n">
-        <v>3.68279051780701</v>
+        <v>3.68279075622559</v>
       </c>
       <c r="H22" t="n">
         <v>5500</v>
@@ -1065,7 +1065,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G24" t="n">
-        <v>3.57476234436035</v>
+        <v>3.57476210594177</v>
       </c>
       <c r="H24" t="n">
         <v>5000</v>
@@ -1268,7 +1268,7 @@
         <v>3.28900003433228</v>
       </c>
       <c r="G31" t="n">
-        <v>3.23005270957947</v>
+        <v>3.23005294799805</v>
       </c>
       <c r="H31" t="n">
         <v>6000</v>
@@ -1326,7 +1326,7 @@
         <v>3.1875</v>
       </c>
       <c r="G33" t="n">
-        <v>3.1303722858429</v>
+        <v>3.13037204742432</v>
       </c>
       <c r="H33" t="n">
         <v>8500</v>
@@ -1384,7 +1384,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>2.92659091949463</v>
+        <v>2.92659115791321</v>
       </c>
       <c r="H35" t="n">
         <v>7000</v>
@@ -1413,7 +1413,7 @@
         <v>2.98699998855591</v>
       </c>
       <c r="G36" t="n">
-        <v>2.93346571922302</v>
+        <v>2.93346548080444</v>
       </c>
       <c r="H36" t="n">
         <v>14000</v>
@@ -1442,7 +1442,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G37" t="n">
-        <v>2.80874156951904</v>
+        <v>2.80874180793762</v>
       </c>
       <c r="H37" t="n">
         <v>12500</v>
@@ -1471,7 +1471,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83820414543152</v>
+        <v>2.83820390701294</v>
       </c>
       <c r="H38" t="n">
         <v>90500</v>
@@ -1500,7 +1500,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82838344573975</v>
+        <v>2.82838320732117</v>
       </c>
       <c r="H39" t="n">
         <v>2000</v>
@@ -1616,7 +1616,7 @@
         <v>3.25</v>
       </c>
       <c r="G43" t="n">
-        <v>3.1917519569397</v>
+        <v>3.19175219535828</v>
       </c>
       <c r="H43" t="n">
         <v>15000</v>
@@ -1674,7 +1674,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G45" t="n">
-        <v>3.32924294471741</v>
+        <v>3.32924270629883</v>
       </c>
       <c r="H45" t="n">
         <v>20500</v>
@@ -1732,7 +1732,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>3.43727111816406</v>
+        <v>3.43727135658264</v>
       </c>
       <c r="H47" t="n">
         <v>10500</v>
@@ -1906,7 +1906,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.29978013038635</v>
+        <v>3.29978036880493</v>
       </c>
       <c r="H53" t="n">
         <v>2500</v>
@@ -1964,7 +1964,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G55" t="n">
-        <v>3.26049733161926</v>
+        <v>3.26049709320068</v>
       </c>
       <c r="H55" t="n">
         <v>500</v>
@@ -2196,7 +2196,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14264798164368</v>
+        <v>3.14264822006226</v>
       </c>
       <c r="H63" t="n">
         <v>2500</v>
@@ -2399,7 +2399,7 @@
         <v>3</v>
       </c>
       <c r="G70" t="n">
-        <v>2.94623255729675</v>
+        <v>2.94623231887817</v>
       </c>
       <c r="H70" t="n">
         <v>2500</v>
@@ -2428,7 +2428,7 @@
         <v>3</v>
       </c>
       <c r="G71" t="n">
-        <v>2.94623255729675</v>
+        <v>2.94623231887817</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>2.94623255729675</v>
+        <v>2.94623231887817</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G95" t="n">
-        <v>3.21139359474182</v>
+        <v>3.21139335632324</v>
       </c>
       <c r="H95" t="n">
         <v>13000</v>
@@ -3472,7 +3472,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>2.92659091949463</v>
+        <v>2.92659115791321</v>
       </c>
       <c r="H107" t="n">
         <v>500</v>
@@ -3501,7 +3501,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>2.84802508354187</v>
+        <v>2.84802484512329</v>
       </c>
       <c r="H108" t="n">
         <v>10000</v>
@@ -3530,7 +3530,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>2.84802508354187</v>
+        <v>2.84802484512329</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>2.92659091949463</v>
+        <v>2.92659115791321</v>
       </c>
       <c r="H110" t="n">
         <v>3500</v>
@@ -3820,7 +3820,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G119" t="n">
-        <v>2.83820414543152</v>
+        <v>2.83820390701294</v>
       </c>
       <c r="H119" t="n">
         <v>4000</v>
@@ -3849,7 +3849,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G120" t="n">
-        <v>2.83820414543152</v>
+        <v>2.83820390701294</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>2.79892086982727</v>
+        <v>2.79892110824585</v>
       </c>
       <c r="H129" t="n">
         <v>8000</v>
@@ -4226,7 +4226,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G133" t="n">
-        <v>2.65160918235779</v>
+        <v>2.65160942077637</v>
       </c>
       <c r="H133" t="n">
         <v>5500</v>
@@ -4371,7 +4371,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G138" t="n">
-        <v>3.10336518287659</v>
+        <v>3.10336494445801</v>
       </c>
       <c r="H138" t="n">
         <v>4500</v>
@@ -4545,7 +4545,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G144" t="n">
-        <v>2.99533653259277</v>
+        <v>2.99533629417419</v>
       </c>
       <c r="H144" t="n">
         <v>3000</v>
@@ -4748,7 +4748,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>3.28995943069458</v>
+        <v>3.28995966911316</v>
       </c>
       <c r="H151" t="n">
         <v>91500</v>
@@ -4864,7 +4864,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>3.14264798164368</v>
+        <v>3.14264822006226</v>
       </c>
       <c r="H155" t="n">
         <v>3500</v>
@@ -30390,6 +30390,35 @@
         <v>1000</v>
       </c>
       <c r="I1035" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1036" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1036" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1036" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1036" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="H1036" t="n">
+        <v>500</v>
+      </c>
+      <c r="I1036" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -30401,13 +30401,13 @@
         <v>46322.3333333333</v>
       </c>
       <c r="C1036" t="n">
-        <v>6</v>
+        <v>6.19999980926514</v>
       </c>
       <c r="D1036" t="n">
-        <v>6</v>
+        <v>6.19999980926514</v>
       </c>
       <c r="E1036" t="n">
-        <v>6</v>
+        <v>6.19999980926514</v>
       </c>
       <c r="F1036" t="n">
         <v>6.19999980926514</v>
@@ -30419,6 +30419,35 @@
         <v>500</v>
       </c>
       <c r="I1036" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1037" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1037" t="n">
+        <v>6</v>
+      </c>
+      <c r="D1037" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1037" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1037" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1037" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2" t="n">
-        <v>3.14264822006226</v>
+        <v>3.14264798164368</v>
       </c>
       <c r="H2" t="n">
         <v>26500</v>
@@ -485,7 +485,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G4" t="n">
-        <v>3.67297005653381</v>
+        <v>3.67296981811523</v>
       </c>
       <c r="H4" t="n">
         <v>18000</v>
@@ -717,7 +717,7 @@
         <v>3.8585000038147</v>
       </c>
       <c r="G12" t="n">
-        <v>3.78934621810913</v>
+        <v>3.78934597969055</v>
       </c>
       <c r="H12" t="n">
         <v>10000</v>
@@ -746,7 +746,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.71716356277466</v>
+        <v>3.71716380119324</v>
       </c>
       <c r="H13" t="n">
         <v>3000</v>
@@ -833,7 +833,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65332841873169</v>
+        <v>3.65332818031311</v>
       </c>
       <c r="H16" t="n">
         <v>9500</v>
@@ -862,7 +862,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G17" t="n">
-        <v>3.65332841873169</v>
+        <v>3.65332818031311</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G18" t="n">
-        <v>3.63368678092957</v>
+        <v>3.63368701934814</v>
       </c>
       <c r="H18" t="n">
         <v>2500</v>
@@ -920,7 +920,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>3.58458304405212</v>
+        <v>3.58458280563354</v>
       </c>
       <c r="H19" t="n">
         <v>4500</v>
@@ -1036,7 +1036,7 @@
         <v>3.64949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>3.5840916633606</v>
+        <v>3.58409190177917</v>
       </c>
       <c r="H23" t="n">
         <v>1500</v>
@@ -1065,7 +1065,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G24" t="n">
-        <v>3.57476210594177</v>
+        <v>3.57476234436035</v>
       </c>
       <c r="H24" t="n">
         <v>5000</v>
@@ -1181,7 +1181,7 @@
         <v>3.50049996376038</v>
       </c>
       <c r="G28" t="n">
-        <v>3.43776226043701</v>
+        <v>3.43776249885559</v>
       </c>
       <c r="H28" t="n">
         <v>500</v>
@@ -1210,7 +1210,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>3.38816738128662</v>
+        <v>3.3881676197052</v>
       </c>
       <c r="H29" t="n">
         <v>3000</v>
@@ -1326,7 +1326,7 @@
         <v>3.1875</v>
       </c>
       <c r="G33" t="n">
-        <v>3.13037204742432</v>
+        <v>3.1303722858429</v>
       </c>
       <c r="H33" t="n">
         <v>8500</v>
@@ -1355,7 +1355,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G34" t="n">
-        <v>2.98747992515564</v>
+        <v>2.98747968673706</v>
       </c>
       <c r="H34" t="n">
         <v>15500</v>
@@ -1384,7 +1384,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>2.92659115791321</v>
+        <v>2.92659091949463</v>
       </c>
       <c r="H35" t="n">
         <v>7000</v>
@@ -1442,7 +1442,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G37" t="n">
-        <v>2.80874180793762</v>
+        <v>2.80874156951904</v>
       </c>
       <c r="H37" t="n">
         <v>12500</v>
@@ -1471,7 +1471,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G38" t="n">
-        <v>2.83820390701294</v>
+        <v>2.83820414543152</v>
       </c>
       <c r="H38" t="n">
         <v>90500</v>
@@ -1500,7 +1500,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G39" t="n">
-        <v>2.82838320732117</v>
+        <v>2.82838344573975</v>
       </c>
       <c r="H39" t="n">
         <v>2000</v>
@@ -1616,7 +1616,7 @@
         <v>3.25</v>
       </c>
       <c r="G43" t="n">
-        <v>3.19175219535828</v>
+        <v>3.1917519569397</v>
       </c>
       <c r="H43" t="n">
         <v>15000</v>
@@ -1645,7 +1645,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.24085569381714</v>
+        <v>3.24085593223572</v>
       </c>
       <c r="H44" t="n">
         <v>51000</v>
@@ -1674,7 +1674,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G45" t="n">
-        <v>3.32924270629883</v>
+        <v>3.32924294471741</v>
       </c>
       <c r="H45" t="n">
         <v>20500</v>
@@ -1703,7 +1703,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>3.37834668159485</v>
+        <v>3.37834644317627</v>
       </c>
       <c r="H46" t="n">
         <v>37500</v>
@@ -1732,7 +1732,7 @@
         <v>3.5</v>
       </c>
       <c r="G47" t="n">
-        <v>3.43727135658264</v>
+        <v>3.43727111816406</v>
       </c>
       <c r="H47" t="n">
         <v>10500</v>
@@ -1790,7 +1790,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G49" t="n">
-        <v>3.33857226371765</v>
+        <v>3.33857250213623</v>
       </c>
       <c r="H49" t="n">
         <v>12500</v>
@@ -1906,7 +1906,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>3.29978036880493</v>
+        <v>3.29978013038635</v>
       </c>
       <c r="H53" t="n">
         <v>2500</v>
@@ -1964,7 +1964,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G55" t="n">
-        <v>3.26049709320068</v>
+        <v>3.26049733161926</v>
       </c>
       <c r="H55" t="n">
         <v>500</v>
@@ -2196,7 +2196,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G63" t="n">
-        <v>3.14264822006226</v>
+        <v>3.14264798164368</v>
       </c>
       <c r="H63" t="n">
         <v>2500</v>
@@ -2225,7 +2225,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.01497793197632</v>
+        <v>3.01497769355774</v>
       </c>
       <c r="H64" t="n">
         <v>2000</v>
@@ -2486,7 +2486,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.01497793197632</v>
+        <v>3.01497769355774</v>
       </c>
       <c r="H73" t="n">
         <v>500</v>
@@ -2515,7 +2515,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G74" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H74" t="n">
         <v>1000</v>
@@ -2718,7 +2718,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>2.9658739566803</v>
+        <v>2.96587419509888</v>
       </c>
       <c r="H81" t="n">
         <v>500</v>
@@ -2834,7 +2834,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H85" t="n">
         <v>1000</v>
@@ -2863,7 +2863,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G90" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H90" t="n">
         <v>1000</v>
@@ -3008,7 +3008,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>3.17211031913757</v>
+        <v>3.17211055755615</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G92" t="n">
-        <v>3.09354400634766</v>
+        <v>3.09354424476624</v>
       </c>
       <c r="H92" t="n">
         <v>1000</v>
@@ -3066,7 +3066,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.09354400634766</v>
+        <v>3.09354424476624</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G95" t="n">
-        <v>3.21139335632324</v>
+        <v>3.21139359474182</v>
       </c>
       <c r="H95" t="n">
         <v>13000</v>
@@ -3211,7 +3211,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>2.9658739566803</v>
+        <v>2.96587419509888</v>
       </c>
       <c r="H98" t="n">
         <v>8000</v>
@@ -3327,7 +3327,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>2.9658739566803</v>
+        <v>2.96587419509888</v>
       </c>
       <c r="H102" t="n">
         <v>4500</v>
@@ -3356,7 +3356,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G103" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H103" t="n">
         <v>1000</v>
@@ -3385,7 +3385,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G104" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G106" t="n">
-        <v>2.95605325698853</v>
+        <v>2.9560534954071</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>2.92659115791321</v>
+        <v>2.92659091949463</v>
       </c>
       <c r="H107" t="n">
         <v>500</v>
@@ -3559,7 +3559,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>2.92659115791321</v>
+        <v>2.92659091949463</v>
       </c>
       <c r="H110" t="n">
         <v>3500</v>
@@ -3588,7 +3588,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G111" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H111" t="n">
         <v>500</v>
@@ -3617,7 +3617,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G112" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G113" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G114" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G115" t="n">
-        <v>2.93641185760498</v>
+        <v>2.9364116191864</v>
       </c>
       <c r="H115" t="n">
         <v>500</v>
@@ -3820,7 +3820,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G119" t="n">
-        <v>2.83820390701294</v>
+        <v>2.83820414543152</v>
       </c>
       <c r="H119" t="n">
         <v>4000</v>
@@ -3849,7 +3849,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G120" t="n">
-        <v>2.83820390701294</v>
+        <v>2.83820414543152</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>2.79892110824585</v>
+        <v>2.79892063140869</v>
       </c>
       <c r="H129" t="n">
         <v>8000</v>
@@ -4139,7 +4139,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>2.710533618927</v>
+        <v>2.71053385734558</v>
       </c>
       <c r="H130" t="n">
         <v>6500</v>
@@ -4168,7 +4168,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G131" t="n">
-        <v>2.74981689453125</v>
+        <v>2.74981713294983</v>
       </c>
       <c r="H131" t="n">
         <v>2000</v>
@@ -4197,7 +4197,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.74981689453125</v>
+        <v>2.74981713294983</v>
       </c>
       <c r="H132" t="n">
         <v>500</v>
@@ -4226,7 +4226,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G133" t="n">
-        <v>2.65160942077637</v>
+        <v>2.65160918235779</v>
       </c>
       <c r="H133" t="n">
         <v>5500</v>
@@ -4255,7 +4255,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.72035479545593</v>
+        <v>2.72035455703735</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4371,7 +4371,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G138" t="n">
-        <v>3.10336494445801</v>
+        <v>3.10336518287659</v>
       </c>
       <c r="H138" t="n">
         <v>4500</v>
@@ -4400,7 +4400,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.09354400634766</v>
+        <v>3.09354424476624</v>
       </c>
       <c r="H139" t="n">
         <v>6000</v>
@@ -4429,7 +4429,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.1328272819519</v>
+        <v>3.13282752037048</v>
       </c>
       <c r="H140" t="n">
         <v>1500</v>
@@ -4487,7 +4487,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G142" t="n">
-        <v>3.01497793197632</v>
+        <v>3.01497769355774</v>
       </c>
       <c r="H142" t="n">
         <v>4000</v>
@@ -4516,7 +4516,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G143" t="n">
-        <v>3.01497793197632</v>
+        <v>3.01497769355774</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G144" t="n">
-        <v>2.99533629417419</v>
+        <v>2.99533653259277</v>
       </c>
       <c r="H144" t="n">
         <v>3000</v>
@@ -4748,7 +4748,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G151" t="n">
-        <v>3.28995966911316</v>
+        <v>3.28995943069458</v>
       </c>
       <c r="H151" t="n">
         <v>91500</v>
@@ -4777,7 +4777,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>3.23103499412537</v>
+        <v>3.23103475570679</v>
       </c>
       <c r="H152" t="n">
         <v>54500</v>
@@ -4806,7 +4806,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>3.23103499412537</v>
+        <v>3.23103475570679</v>
       </c>
       <c r="H153" t="n">
         <v>13500</v>
@@ -4835,7 +4835,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>3.15246891975403</v>
+        <v>3.15246868133545</v>
       </c>
       <c r="H154" t="n">
         <v>5500</v>
@@ -4864,7 +4864,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G155" t="n">
-        <v>3.14264822006226</v>
+        <v>3.14264798164368</v>
       </c>
       <c r="H155" t="n">
         <v>3500</v>
@@ -4951,7 +4951,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G158" t="n">
-        <v>3.05426120758057</v>
+        <v>3.05426096916199</v>
       </c>
       <c r="H158" t="n">
         <v>3500</v>
@@ -4980,7 +4980,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G159" t="n">
-        <v>3.05426120758057</v>
+        <v>3.05426096916199</v>
       </c>
       <c r="H159" t="n">
         <v>500</v>
@@ -30448,6 +30448,35 @@
         <v>2000</v>
       </c>
       <c r="I1037" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1038" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1038" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="D1038" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1038" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1038" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1038" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCH.MI.xlsx
+++ b/data/FCH.MI.xlsx
@@ -572,7 +572,7 @@
         <v>3.75</v>
       </c>
       <c r="G7" t="n">
-        <v>3.68279075622559</v>
+        <v>3.68279051780701</v>
       </c>
       <c r="H7" t="n">
         <v>5500</v>
@@ -659,7 +659,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G10" t="n">
-        <v>3.89884781837463</v>
+        <v>3.89884757995605</v>
       </c>
       <c r="H10" t="n">
         <v>36500</v>
@@ -717,7 +717,7 @@
         <v>3.8585000038147</v>
       </c>
       <c r="G12" t="n">
-        <v>3.78934597969055</v>
+        <v>3.78934621810913</v>
       </c>
       <c r="H12" t="n">
         <v>10000</v>
@@ -746,7 +746,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.71716380119324</v>
+        <v>3.71716356277466</v>
       </c>
       <c r="H13" t="n">
         <v>3000</v>
@@ -775,7 +775,7 @@
         <v>3.75</v>
       </c>
       <c r="G14" t="n">
-        <v>3.68279075622559</v>
+        <v>3.68279051780701</v>
       </c>
       <c r="H14" t="n">
         <v>500</v>
@@ -833,7 +833,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65332818031311</v>
+        <v>3.65332841873169</v>
       </c>
       <c r="H16" t="n">
         <v>9500</v>
@@ -862,7 +862,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G17" t="n">
-        <v>3.65332818031311</v>
+        <v>3.65332841873169</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>3.58458280563354</v>
+        <v>3.58458304405212</v>
       </c>
       <c r="H19" t="n">
         <v>4500</v>
@@ -1007,7 +1007,7 @@
         <v>3.75</v>
       </c>
       <c r="G22" t="n">
-        <v>3.68279075622559</v>
+        <v>3.68279051780701</v>
       </c>
       <c r="H22" t="n">
         <v>5500</v>
@@ -1036,7 +1036,7 @@
         <v>3.64949989318848</v>
       </c>
       <c r="G23" t="n">
-        <v>3.58409190177917</v>
+        <v>3.5840916633606</v>
       </c>
       <c r="H23" t="n">
         <v>1500</v>
@@ -1181,7 +1181,7 @@
         <v>3.50049996376038</v>
       </c>
       <c r="G28" t="n">
-        <v>3.43776249885559</v>
+        <v>3.43776226043701</v>
       </c>
       <c r="H28" t="n">
         <v>500</v>
@@ -1210,7 +1210,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G29" t="n">
-        <v>3.3881676197052</v>
+        <v>3.38816738128662</v>
       </c>
       <c r="H29" t="n">
         <v>3000</v>
@@ -1268,7 +1268,7 @@
         <v>3.28900003433228</v>
       </c>
       <c r="G31" t="n">
-        <v>3.23005294799805</v>
+        <v>3.23005270957947</v>
       </c>
       <c r="H31" t="n">
         <v>6000</v>
@@ -1355,7 +1355,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G34" t="n">
-        <v>2.98747968673706</v>
+        <v>2.98747992515564</v>
       </c>
       <c r="H34" t="n">
         <v>15500</v>
@@ -1413,7 +1413,7 @@
         <v>2.98699998855591</v>
       </c>
       <c r="G36" t="n">
-        <v>2.93346548080444</v>
+        <v>2.93346571922302</v>
       </c>
       <c r="H36" t="n">
         <v>14000</v>
@@ -1645,7 +1645,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G44" t="n">
-        <v>3.24085593223572</v>
+        <v>3.24085569381714</v>
       </c>
       <c r="H44" t="n">
         <v>51000</v>
@@ -1703,7 +1703,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G46" t="n">
-        <v>3.37834644317627</v>
+        <v>3.37834668159485</v>
       </c>
       <c r="H46" t="n">
         <v>37500</v>
@@ -1790,7 +1790,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G49" t="n">
-        <v>3.33857250213623</v>
+        <v>3.33857226371765</v>
       </c>
       <c r="H49" t="n">
         <v>12500</v>
@@ -2225,7 +2225,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.01497769355774</v>
+        <v>3.01497793197632</v>
       </c>
       <c r="H64" t="n">
         <v>2000</v>
@@ -2399,7 +2399,7 @@
         <v>3</v>
       </c>
       <c r="G70" t="n">
-        <v>2.94623231887817</v>
+        <v>2.94623255729675</v>
       </c>
       <c r="H70" t="n">
         <v>2500</v>
@@ -2428,7 +2428,7 @@
         <v>3</v>
       </c>
       <c r="G71" t="n">
-        <v>2.94623231887817</v>
+        <v>2.94623255729675</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>2.94623231887817</v>
+        <v>2.94623255729675</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.01497769355774</v>
+        <v>3.01497793197632</v>
       </c>
       <c r="H73" t="n">
         <v>500</v>
@@ -2515,7 +2515,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G74" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H74" t="n">
         <v>1000</v>
@@ -2718,7 +2718,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H81" t="n">
         <v>500</v>
@@ -2834,7 +2834,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H85" t="n">
         <v>1000</v>
@@ -2863,7 +2863,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G89" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G90" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H90" t="n">
         <v>1000</v>
@@ -3008,7 +3008,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G91" t="n">
-        <v>3.17211055755615</v>
+        <v>3.17211031913757</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G92" t="n">
-        <v>3.09354424476624</v>
+        <v>3.09354400634766</v>
       </c>
       <c r="H92" t="n">
         <v>1000</v>
@@ -3066,7 +3066,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G93" t="n">
-        <v>3.09354424476624</v>
+        <v>3.09354400634766</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H98" t="n">
         <v>8000</v>
@@ -3327,7 +3327,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G102" t="n">
-        <v>2.96587419509888</v>
+        <v>2.9658739566803</v>
       </c>
       <c r="H102" t="n">
         <v>4500</v>
@@ -3356,7 +3356,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G103" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H103" t="n">
         <v>1000</v>
@@ -3385,7 +3385,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G104" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G105" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G106" t="n">
-        <v>2.9560534954071</v>
+        <v>2.95605325698853</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G108" t="n">
-        <v>2.84802484512329</v>
+        <v>2.84802508354187</v>
       </c>
       <c r="H108" t="n">
         <v>10000</v>
@@ -3530,7 +3530,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G109" t="n">
-        <v>2.84802484512329</v>
+        <v>2.84802508354187</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G111" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H111" t="n">
         <v>500</v>
@@ -3617,7 +3617,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G112" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G113" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G114" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G115" t="n">
-        <v>2.9364116191864</v>
+        <v>2.93641185760498</v>
       </c>
       <c r="H115" t="n">
         <v>500</v>
@@ -4110,7 +4110,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G129" t="n">
-        <v>2.79892063140869</v>
+        <v>2.79892086982727</v>
       </c>
       <c r="H129" t="n">
         <v>8000</v>
@@ -4139,7 +4139,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G130" t="n">
-        <v>2.71053385734558</v>
+        <v>2.710533618927</v>
       </c>
       <c r="H130" t="n">
         <v>6500</v>
@@ -4168,7 +4168,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G131" t="n">
-        <v>2.74981713294983</v>
+        <v>2.74981689453125</v>
       </c>
       <c r="H131" t="n">
         <v>2000</v>
@@ -4197,7 +4197,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G132" t="n">
-        <v>2.74981713294983</v>
+        <v>2.74981689453125</v>
       </c>
       <c r="H132" t="n">
         <v>500</v>
@@ -4255,7 +4255,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.72035455703735</v>
+        <v>2.72035479545593</v>
       </c>
       <c r="H134" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G139" t="n">
-        <v>3.09354424476624</v>
+        <v>3.09354400634766</v>
       </c>
       <c r="H139" t="n">
         <v>6000</v>
@@ -4429,7 +4429,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G140" t="n">
-        <v>3.13282752037048</v>
+        <v>3.1328272819519</v>
       </c>
       <c r="H140" t="n">
         <v>1500</v>
@@ -4487,7 +4487,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G142" t="n">
-        <v>3.01497769355774</v>
+        <v>3.01497793197632</v>
       </c>
       <c r="H142" t="n">
         <v>4000</v>
@@ -4516,7 +4516,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G143" t="n">
-        <v>3.01497769355774</v>
+        <v>3.01497793197632</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>3.23103475570679</v>
+        <v>3.23103499412537</v>
       </c>
       <c r="H152" t="n">
         <v>54500</v>
@@ -4806,7 +4806,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G153" t="n">
-        <v>3.23103475570679</v>
+        <v>3.23103499412537</v>
       </c>
       <c r="H153" t="n">
         <v>13500</v>
@@ -4835,7 +4835,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>3.15246868133545</v>
+        <v>3.15246891975403</v>
       </c>
       <c r="H154" t="n">
         <v>5500</v>
@@ -4951,7 +4951,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G158" t="n">
-        <v>3.05426096916199</v>
+        <v>3.05426120758057</v>
       </c>
       <c r="H158" t="n">
         <v>3500</v>
@@ -4980,7 +4980,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G159" t="n">
-        <v>3.05426096916199</v>
+        <v>3.05426120758057</v>
       </c>
       <c r="H159" t="n">
         <v>500</v>
@@ -30477,6 +30477,35 @@
         <v>3000</v>
       </c>
       <c r="I1038" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1039" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1039" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="D1039" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="E1039" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1039" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I1039" t="s">
         <v>9</v>
       </c>
     </row>
